--- a/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
@@ -8,26 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D563967-F778-4FC4-9E1E-6F1C6597344A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098EC3CE-315C-4E4A-B3FE-06322FA62054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -82,484 +73,484 @@
     <t>MAP&lt;INT:LONG&gt;_C_S</t>
   </si>
   <si>
-    <t>3010101:1_3020101:1_3030101:20</t>
-  </si>
-  <si>
-    <t>3010101:2_3020101:2_3030101:40</t>
-  </si>
-  <si>
-    <t>3010101:3_3020101:3_3030101:60</t>
-  </si>
-  <si>
-    <t>3010101:4_3020101:4_3030101:80</t>
-  </si>
-  <si>
-    <t>3010101:5_3020101:5_3030101:104</t>
-  </si>
-  <si>
-    <t>3010101:7_3020101:7_3030101:137</t>
-  </si>
-  <si>
-    <t>3010101:9_3020101:9_3030101:180</t>
-  </si>
-  <si>
-    <t>3010101:12_3020101:12_3030101:235</t>
-  </si>
-  <si>
-    <t>3010101:15_3020101:15_3030101:302</t>
-  </si>
-  <si>
-    <t>3010101:20_3020101:20_3030101:401</t>
-  </si>
-  <si>
-    <t>3010101:29_3020101:29_3030101:581</t>
-  </si>
-  <si>
-    <t>3010101:43_3020101:43_3030101:866</t>
-  </si>
-  <si>
-    <t>3010101:64_3020101:64_3030101:1283</t>
-  </si>
-  <si>
-    <t>3010101:93_3020101:93_3030101:1859</t>
-  </si>
-  <si>
-    <t>3010101:131_3020101:131_3030101:2620</t>
-  </si>
-  <si>
-    <t>3010101:180_3020101:180_3030101:3593</t>
-  </si>
-  <si>
-    <t>3010101:241_3020101:241_3030101:4805</t>
-  </si>
-  <si>
-    <t>3010101:315_3020101:315_3030101:6282</t>
-  </si>
-  <si>
-    <t>3010101:403_3020101:403_3030101:8051</t>
-  </si>
-  <si>
-    <t>3010101:507_3020101:507_3030101:10139</t>
-  </si>
-  <si>
-    <t>3010101:629_3020101:629_3030101:12572</t>
-  </si>
-  <si>
-    <t>3010101:769_3020101:769_3030101:15377</t>
-  </si>
-  <si>
-    <t>3010101:929_3020101:929_3030101:18581</t>
-  </si>
-  <si>
-    <t>3010101:1110_3020101:1110_3030101:22210</t>
-  </si>
-  <si>
-    <t>3010101:1314_3020101:1314_3030101:26291</t>
-  </si>
-  <si>
-    <t>3010101:1542_3020101:1542_3030101:30851</t>
-  </si>
-  <si>
-    <t>3010101:1795_3020101:1795_3030101:35916</t>
-  </si>
-  <si>
-    <t>3010101:2075_3020101:2075_3030101:41513</t>
-  </si>
-  <si>
-    <t>3010101:2383_3020101:2383_3030101:47669</t>
-  </si>
-  <si>
-    <t>3010101:2720_3020101:2720_3030101:54410</t>
-  </si>
-  <si>
-    <t>3010101:3088_3020101:3088_3030101:61763</t>
-  </si>
-  <si>
-    <t>3010101:3488_3020101:3488_3030101:69755</t>
-  </si>
-  <si>
-    <t>3010101:3921_3020101:3921_3030101:78412</t>
-  </si>
-  <si>
-    <t>3010101:4388_3020101:4388_3030101:87761</t>
-  </si>
-  <si>
-    <t>3010101:4891_3020101:4891_3030101:97829</t>
-  </si>
-  <si>
-    <t>3010101:5432_3020101:5432_3030101:108642</t>
-  </si>
-  <si>
-    <t>3010101:6011_3020101:6011_3030101:120227</t>
-  </si>
-  <si>
-    <t>3010101:6630_3020101:6630_3030101:132611</t>
-  </si>
-  <si>
-    <t>3010101:7290_3020101:7290_3030101:145820</t>
-  </si>
-  <si>
-    <t>3010101:7993_3020101:7993_3030101:159881</t>
-  </si>
-  <si>
-    <t>3010101:8740_3020101:8740_3030101:174821</t>
-  </si>
-  <si>
-    <t>3010101:9532_3020101:9532_3030101:190666</t>
-  </si>
-  <si>
-    <t>3010101:10371_3020101:10371_3030101:207443</t>
-  </si>
-  <si>
-    <t>3010101:11258_3020101:11258_3030101:225179</t>
-  </si>
-  <si>
-    <t>3010101:12194_3020101:12194_3030101:243900</t>
-  </si>
-  <si>
-    <t>3010101:13181_3020101:13181_3030101:263633</t>
-  </si>
-  <si>
-    <t>3010101:14220_3020101:14220_3030101:284406</t>
-  </si>
-  <si>
-    <t>3010101:15313_3020101:15313_3030101:306273</t>
-  </si>
-  <si>
-    <t>3010101:16463_3020101:16463_3030101:329273</t>
-  </si>
-  <si>
-    <t>3010101:17672_3020101:17672_3030101:353446</t>
-  </si>
-  <si>
-    <t>3010101:18942_3020101:18942_3030101:378846</t>
-  </si>
-  <si>
-    <t>3010101:20275_3020101:20275_3030101:405513</t>
-  </si>
-  <si>
-    <t>3010101:21674_3020101:21674_3030101:433500</t>
-  </si>
-  <si>
-    <t>3010101:23142_3020101:23142_3030101:462860</t>
-  </si>
-  <si>
-    <t>3010101:24681_3020101:24681_3030101:493647</t>
-  </si>
-  <si>
-    <t>3010101:26294_3020101:26294_3030101:525914</t>
-  </si>
-  <si>
-    <t>3010101:27984_3020101:27984_3030101:559714</t>
-  </si>
-  <si>
-    <t>3010101:29753_3020101:29753_3030101:595101</t>
-  </si>
-  <si>
-    <t>3010101:31605_3020101:31605_3030101:632141</t>
-  </si>
-  <si>
-    <t>3010101:33542_3020101:33542_3030101:670888</t>
-  </si>
-  <si>
-    <t>3010101:35568_3020101:35568_3030101:711408</t>
-  </si>
-  <si>
-    <t>3010101:37686_3020101:37686_3030101:753768</t>
-  </si>
-  <si>
-    <t>3010101:39899_3020101:39899_3030101:798021</t>
-  </si>
-  <si>
-    <t>3010101:42210_3020101:42210_3030101:844234</t>
-  </si>
-  <si>
-    <t>3010101:44623_3020101:44623_3030101:892487</t>
-  </si>
-  <si>
-    <t>3010101:47141_3020101:47141_3030101:942847</t>
-  </si>
-  <si>
-    <t>3010101:49768_3020101:49768_3030101:995380</t>
-  </si>
-  <si>
-    <t>3010101:52507_3020101:52507_3030101:1050167</t>
-  </si>
-  <si>
-    <t>3010101:55363_3020101:55363_3030101:1107287</t>
-  </si>
-  <si>
-    <t>3010101:58340_3020101:58340_3030101:1166820</t>
-  </si>
-  <si>
-    <t>3010101:61441_3020101:61441_3030101:1228847</t>
-  </si>
-  <si>
-    <t>3010101:64671_3020101:64671_3030101:1293447</t>
-  </si>
-  <si>
-    <t>3010101:68034_3020101:68034_3030101:1360700</t>
-  </si>
-  <si>
-    <t>3010101:71534_3020101:71534_3030101:1430700</t>
-  </si>
-  <si>
-    <t>3010101:75176_3020101:75176_3030101:1503540</t>
-  </si>
-  <si>
-    <t>3010101:78965_3020101:78965_3030101:1579313</t>
-  </si>
-  <si>
-    <t>3010101:82905_3020101:82905_3030101:1658113</t>
-  </si>
-  <si>
-    <t>3010101:87001_3020101:87001_3030101:1740033</t>
-  </si>
-  <si>
-    <t>3010101:91258_3020101:91258_3030101:1825180</t>
-  </si>
-  <si>
-    <t>3010101:95682_3020101:95682_3030101:1913660</t>
-  </si>
-  <si>
-    <t>3010101:100278_3020101:100278_3030101:2005580</t>
-  </si>
-  <si>
-    <t>3010101:105051_3020101:105051_3030101:2101047</t>
-  </si>
-  <si>
-    <t>3010101:110007_3020101:110007_3030101:2200167</t>
-  </si>
-  <si>
-    <t>3010101:115007_3020101:115007_3030101:2300167</t>
-  </si>
-  <si>
-    <t>3010101:120007_3020101:120007_3030101:2400167</t>
-  </si>
-  <si>
-    <t>3010101:125007_3020101:125007_3030101:2500167</t>
-  </si>
-  <si>
-    <t>3010101:130007_3020101:130007_3030101:2600167</t>
-  </si>
-  <si>
-    <t>3010101:135007_3020101:135007_3030101:2700167</t>
-  </si>
-  <si>
-    <t>3010101:140007_3020101:140007_3030101:2800167</t>
-  </si>
-  <si>
-    <t>3010101:145007_3020101:145007_3030101:2900167</t>
-  </si>
-  <si>
-    <t>3010101:150007_3020101:150007_3030101:3000167</t>
-  </si>
-  <si>
-    <t>3010101:155007_3020101:155007_3030101:3100167</t>
-  </si>
-  <si>
-    <t>3010101:160007_3020101:160007_3030101:3200167</t>
-  </si>
-  <si>
-    <t>3010101:165007_3020101:165007_3030101:3300167</t>
-  </si>
-  <si>
-    <t>3010101:170007_3020101:170007_3030101:3400167</t>
-  </si>
-  <si>
-    <t>3010101:175007_3020101:175007_3030101:3500167</t>
-  </si>
-  <si>
-    <t>3010101:180007_3020101:180007_3030101:3600167</t>
-  </si>
-  <si>
-    <t>3010101:185007_3020101:185007_3030101:3700167</t>
-  </si>
-  <si>
-    <t>3010101:190007_3020101:190007_3030101:3800167</t>
-  </si>
-  <si>
-    <t>3010101:195007_3020101:195007_3030101:3900167</t>
-  </si>
-  <si>
-    <t>3010101:200007_3020101:200007_3030101:4000167</t>
-  </si>
-  <si>
-    <t>3010101:205007_3020101:205007_3030101:4100167</t>
-  </si>
-  <si>
-    <t>3010101:210007_3020101:210007_3030101:4200167</t>
-  </si>
-  <si>
-    <t>3010101:215007_3020101:215007_3030101:4300167</t>
-  </si>
-  <si>
-    <t>3010101:220007_3020101:220007_3030101:4400167</t>
-  </si>
-  <si>
-    <t>3010101:225007_3020101:225007_3030101:4500167</t>
-  </si>
-  <si>
-    <t>3010101:230007_3020101:230007_3030101:4600167</t>
-  </si>
-  <si>
-    <t>3010101:235007_3020101:235007_3030101:4700167</t>
-  </si>
-  <si>
-    <t>3010101:240007_3020101:240007_3030101:4800167</t>
-  </si>
-  <si>
-    <t>3010101:245007_3020101:245007_3030101:4900167</t>
-  </si>
-  <si>
-    <t>3010101:250007_3020101:250007_3030101:5000167</t>
-  </si>
-  <si>
-    <t>3010101:255007_3020101:255007_3030101:5100167</t>
-  </si>
-  <si>
-    <t>3010101:260007_3020101:260007_3030101:5200167</t>
-  </si>
-  <si>
-    <t>3010101:265007_3020101:265007_3030101:5300167</t>
-  </si>
-  <si>
-    <t>3010101:270007_3020101:270007_3030101:5400167</t>
-  </si>
-  <si>
-    <t>3010101:275007_3020101:275007_3030101:5500167</t>
-  </si>
-  <si>
-    <t>3010101:280007_3020101:280007_3030101:5600167</t>
-  </si>
-  <si>
-    <t>3010101:285007_3020101:285007_3030101:5700167</t>
-  </si>
-  <si>
-    <t>3010101:290007_3020101:290007_3030101:5800167</t>
-  </si>
-  <si>
-    <t>3010101:295007_3020101:295007_3030101:5900167</t>
-  </si>
-  <si>
-    <t>3010101:300007_3020101:300007_3030101:6000167</t>
-  </si>
-  <si>
-    <t>3010101:305007_3020101:305007_3030101:6100167</t>
-  </si>
-  <si>
-    <t>3010101:310007_3020101:310007_3030101:6200167</t>
-  </si>
-  <si>
-    <t>3010101:315007_3020101:315007_3030101:6300167</t>
-  </si>
-  <si>
-    <t>3010101:320007_3020101:320007_3030101:6400167</t>
-  </si>
-  <si>
-    <t>3010101:325007_3020101:325007_3030101:6500167</t>
-  </si>
-  <si>
-    <t>3010101:330007_3020101:330007_3030101:6600167</t>
-  </si>
-  <si>
-    <t>3010101:335007_3020101:335007_3030101:6700167</t>
-  </si>
-  <si>
-    <t>3010101:340007_3020101:340007_3030101:6800167</t>
-  </si>
-  <si>
-    <t>3010101:345007_3020101:345007_3030101:6900167</t>
-  </si>
-  <si>
-    <t>3010101:350007_3020101:350007_3030101:7000167</t>
-  </si>
-  <si>
-    <t>3010101:355007_3020101:355007_3030101:7100167</t>
-  </si>
-  <si>
-    <t>3010101:360007_3020101:360007_3030101:7200167</t>
-  </si>
-  <si>
-    <t>3010101:365007_3020101:365007_3030101:7300167</t>
-  </si>
-  <si>
-    <t>3010101:370007_3020101:370007_3030101:7400167</t>
-  </si>
-  <si>
-    <t>3010101:375007_3020101:375007_3030101:7500167</t>
-  </si>
-  <si>
-    <t>3010101:380007_3020101:380007_3030101:7600167</t>
-  </si>
-  <si>
-    <t>3010101:385007_3020101:385007_3030101:7700167</t>
-  </si>
-  <si>
-    <t>3010101:390007_3020101:390007_3030101:7800167</t>
-  </si>
-  <si>
-    <t>3010101:395007_3020101:395007_3030101:7900167</t>
-  </si>
-  <si>
-    <t>3010101:400007_3020101:400007_3030101:8000167</t>
-  </si>
-  <si>
-    <t>3010101:405007_3020101:405007_3030101:8100167</t>
-  </si>
-  <si>
-    <t>3010101:410007_3020101:410007_3030101:8200167</t>
-  </si>
-  <si>
-    <t>3010101:415007_3020101:415007_3030101:8300167</t>
-  </si>
-  <si>
-    <t>3010101:420007_3020101:420007_3030101:8400167</t>
-  </si>
-  <si>
-    <t>3010101:425007_3020101:425007_3030101:8500167</t>
-  </si>
-  <si>
-    <t>3010101:430007_3020101:430007_3030101:8600167</t>
-  </si>
-  <si>
-    <t>3010101:435007_3020101:435007_3030101:8700167</t>
-  </si>
-  <si>
-    <t>3010101:440007_3020101:440007_3030101:8800167</t>
-  </si>
-  <si>
-    <t>3010101:445007_3020101:445007_3030101:8900167</t>
-  </si>
-  <si>
-    <t>3010101:450007_3020101:450007_3030101:9000167</t>
-  </si>
-  <si>
-    <t>3010101:455007_3020101:455007_3030101:9100167</t>
-  </si>
-  <si>
-    <t>3010101:460007_3020101:460007_3030101:9200167</t>
-  </si>
-  <si>
-    <t>3010101:465007_3020101:465007_3030101:9300167</t>
-  </si>
-  <si>
-    <t>3010101:470007_3020101:470007_3030101:9400167</t>
-  </si>
-  <si>
-    <t>3010101:475007_3020101:475007_3030101:9500167</t>
-  </si>
-  <si>
-    <t>3010101:480007_3020101:480007_3030101:9600167</t>
-  </si>
-  <si>
-    <t>3010101:485007_3020101:485007_3030101:9700167</t>
-  </si>
-  <si>
-    <t>3010101:490007_3020101:490007_3030101:9800167</t>
-  </si>
-  <si>
-    <t>3010101:495007_3020101:495007_3030101:9900167</t>
+    <t>9101:50</t>
+  </si>
+  <si>
+    <t>9101:100</t>
+  </si>
+  <si>
+    <t>9101:150</t>
+  </si>
+  <si>
+    <t>9101:200</t>
+  </si>
+  <si>
+    <t>9101:250</t>
+  </si>
+  <si>
+    <t>9101:300</t>
+  </si>
+  <si>
+    <t>9101:350</t>
+  </si>
+  <si>
+    <t>9101:400</t>
+  </si>
+  <si>
+    <t>9101:450</t>
+  </si>
+  <si>
+    <t>9101:500</t>
+  </si>
+  <si>
+    <t>9101:550</t>
+  </si>
+  <si>
+    <t>9101:600</t>
+  </si>
+  <si>
+    <t>9101:650</t>
+  </si>
+  <si>
+    <t>9101:700</t>
+  </si>
+  <si>
+    <t>9101:750</t>
+  </si>
+  <si>
+    <t>9101:800</t>
+  </si>
+  <si>
+    <t>9101:850</t>
+  </si>
+  <si>
+    <t>9101:900</t>
+  </si>
+  <si>
+    <t>9101:950</t>
+  </si>
+  <si>
+    <t>9101:1000</t>
+  </si>
+  <si>
+    <t>9101:1050</t>
+  </si>
+  <si>
+    <t>9101:1100</t>
+  </si>
+  <si>
+    <t>9101:1150</t>
+  </si>
+  <si>
+    <t>9101:1200</t>
+  </si>
+  <si>
+    <t>9101:1250</t>
+  </si>
+  <si>
+    <t>9101:1300</t>
+  </si>
+  <si>
+    <t>9101:1350</t>
+  </si>
+  <si>
+    <t>9101:1400</t>
+  </si>
+  <si>
+    <t>9101:1450</t>
+  </si>
+  <si>
+    <t>9101:1500</t>
+  </si>
+  <si>
+    <t>9101:1550</t>
+  </si>
+  <si>
+    <t>9101:1600</t>
+  </si>
+  <si>
+    <t>9101:1650</t>
+  </si>
+  <si>
+    <t>9101:1700</t>
+  </si>
+  <si>
+    <t>9101:1750</t>
+  </si>
+  <si>
+    <t>9101:1800</t>
+  </si>
+  <si>
+    <t>9101:1850</t>
+  </si>
+  <si>
+    <t>9101:1900</t>
+  </si>
+  <si>
+    <t>9101:1950</t>
+  </si>
+  <si>
+    <t>9101:2000</t>
+  </si>
+  <si>
+    <t>9101:2050</t>
+  </si>
+  <si>
+    <t>9101:2100</t>
+  </si>
+  <si>
+    <t>9101:2150</t>
+  </si>
+  <si>
+    <t>9101:2200</t>
+  </si>
+  <si>
+    <t>9101:2250</t>
+  </si>
+  <si>
+    <t>9101:2300</t>
+  </si>
+  <si>
+    <t>9101:2350</t>
+  </si>
+  <si>
+    <t>9101:2400</t>
+  </si>
+  <si>
+    <t>9101:2450</t>
+  </si>
+  <si>
+    <t>9101:2500</t>
+  </si>
+  <si>
+    <t>9101:2550</t>
+  </si>
+  <si>
+    <t>9101:2600</t>
+  </si>
+  <si>
+    <t>9101:2650</t>
+  </si>
+  <si>
+    <t>9101:2700</t>
+  </si>
+  <si>
+    <t>9101:2750</t>
+  </si>
+  <si>
+    <t>9101:2800</t>
+  </si>
+  <si>
+    <t>9101:2850</t>
+  </si>
+  <si>
+    <t>9101:2900</t>
+  </si>
+  <si>
+    <t>9101:2950</t>
+  </si>
+  <si>
+    <t>9101:3000</t>
+  </si>
+  <si>
+    <t>9101:3050</t>
+  </si>
+  <si>
+    <t>9101:3100</t>
+  </si>
+  <si>
+    <t>9101:3150</t>
+  </si>
+  <si>
+    <t>9101:3200</t>
+  </si>
+  <si>
+    <t>9101:3250</t>
+  </si>
+  <si>
+    <t>9101:3300</t>
+  </si>
+  <si>
+    <t>9101:3350</t>
+  </si>
+  <si>
+    <t>9101:3400</t>
+  </si>
+  <si>
+    <t>9101:3450</t>
+  </si>
+  <si>
+    <t>9101:3500</t>
+  </si>
+  <si>
+    <t>9101:3550</t>
+  </si>
+  <si>
+    <t>9101:3600</t>
+  </si>
+  <si>
+    <t>9101:3650</t>
+  </si>
+  <si>
+    <t>9101:3700</t>
+  </si>
+  <si>
+    <t>9101:3750</t>
+  </si>
+  <si>
+    <t>9101:3800</t>
+  </si>
+  <si>
+    <t>9101:3850</t>
+  </si>
+  <si>
+    <t>9101:3900</t>
+  </si>
+  <si>
+    <t>9101:3950</t>
+  </si>
+  <si>
+    <t>9101:4000</t>
+  </si>
+  <si>
+    <t>9101:4050</t>
+  </si>
+  <si>
+    <t>9101:4100</t>
+  </si>
+  <si>
+    <t>9101:4150</t>
+  </si>
+  <si>
+    <t>9101:4200</t>
+  </si>
+  <si>
+    <t>9101:4250</t>
+  </si>
+  <si>
+    <t>9101:4300</t>
+  </si>
+  <si>
+    <t>9101:4350</t>
+  </si>
+  <si>
+    <t>9101:4400</t>
+  </si>
+  <si>
+    <t>9101:4450</t>
+  </si>
+  <si>
+    <t>9101:4500</t>
+  </si>
+  <si>
+    <t>9101:4550</t>
+  </si>
+  <si>
+    <t>9101:4600</t>
+  </si>
+  <si>
+    <t>9101:4650</t>
+  </si>
+  <si>
+    <t>9101:4700</t>
+  </si>
+  <si>
+    <t>9101:4750</t>
+  </si>
+  <si>
+    <t>9101:4800</t>
+  </si>
+  <si>
+    <t>9101:4850</t>
+  </si>
+  <si>
+    <t>9101:4900</t>
+  </si>
+  <si>
+    <t>9101:4950</t>
+  </si>
+  <si>
+    <t>9101:5000</t>
+  </si>
+  <si>
+    <t>9101:5050</t>
+  </si>
+  <si>
+    <t>9101:5100</t>
+  </si>
+  <si>
+    <t>9101:5150</t>
+  </si>
+  <si>
+    <t>9101:5200</t>
+  </si>
+  <si>
+    <t>9101:5250</t>
+  </si>
+  <si>
+    <t>9101:5300</t>
+  </si>
+  <si>
+    <t>9101:5350</t>
+  </si>
+  <si>
+    <t>9101:5400</t>
+  </si>
+  <si>
+    <t>9101:5450</t>
+  </si>
+  <si>
+    <t>9101:5500</t>
+  </si>
+  <si>
+    <t>9101:5550</t>
+  </si>
+  <si>
+    <t>9101:5600</t>
+  </si>
+  <si>
+    <t>9101:5650</t>
+  </si>
+  <si>
+    <t>9101:5700</t>
+  </si>
+  <si>
+    <t>9101:5750</t>
+  </si>
+  <si>
+    <t>9101:5800</t>
+  </si>
+  <si>
+    <t>9101:5850</t>
+  </si>
+  <si>
+    <t>9101:5900</t>
+  </si>
+  <si>
+    <t>9101:5950</t>
+  </si>
+  <si>
+    <t>9101:6000</t>
+  </si>
+  <si>
+    <t>9101:6050</t>
+  </si>
+  <si>
+    <t>9101:6100</t>
+  </si>
+  <si>
+    <t>9101:6150</t>
+  </si>
+  <si>
+    <t>9101:6200</t>
+  </si>
+  <si>
+    <t>9101:6250</t>
+  </si>
+  <si>
+    <t>9101:6300</t>
+  </si>
+  <si>
+    <t>9101:6350</t>
+  </si>
+  <si>
+    <t>9101:6400</t>
+  </si>
+  <si>
+    <t>9101:6450</t>
+  </si>
+  <si>
+    <t>9101:6500</t>
+  </si>
+  <si>
+    <t>9101:6550</t>
+  </si>
+  <si>
+    <t>9101:6600</t>
+  </si>
+  <si>
+    <t>9101:6650</t>
+  </si>
+  <si>
+    <t>9101:6700</t>
+  </si>
+  <si>
+    <t>9101:6750</t>
+  </si>
+  <si>
+    <t>9101:6800</t>
+  </si>
+  <si>
+    <t>9101:6850</t>
+  </si>
+  <si>
+    <t>9101:6900</t>
+  </si>
+  <si>
+    <t>9101:6950</t>
+  </si>
+  <si>
+    <t>9101:7000</t>
+  </si>
+  <si>
+    <t>9101:7050</t>
+  </si>
+  <si>
+    <t>9101:7100</t>
+  </si>
+  <si>
+    <t>9101:7150</t>
+  </si>
+  <si>
+    <t>9101:7200</t>
+  </si>
+  <si>
+    <t>9101:7250</t>
+  </si>
+  <si>
+    <t>9101:7300</t>
+  </si>
+  <si>
+    <t>9101:7350</t>
+  </si>
+  <si>
+    <t>9101:7400</t>
+  </si>
+  <si>
+    <t>9101:7450</t>
+  </si>
+  <si>
+    <t>9101:7500</t>
+  </si>
+  <si>
+    <t>9101:7550</t>
+  </si>
+  <si>
+    <t>9101:7600</t>
+  </si>
+  <si>
+    <t>9101:7650</t>
+  </si>
+  <si>
+    <t>9101:7700</t>
+  </si>
+  <si>
+    <t>9101:7750</t>
+  </si>
+  <si>
+    <t>9101:7800</t>
+  </si>
+  <si>
+    <t>9101:7850</t>
+  </si>
+  <si>
+    <t>9101:7900</t>
+  </si>
+  <si>
+    <t>9101:7950</t>
+  </si>
+  <si>
+    <t>9101:8000</t>
   </si>
 </sst>
 </file>
@@ -957,10 +948,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>80</v>
+        <v>10000</v>
       </c>
       <c r="C5" s="1">
-        <v>80</v>
+        <v>10000</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -971,10 +962,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="C6" s="1">
-        <v>330</v>
+        <v>10450</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>13</v>
@@ -985,10 +976,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="C7" s="1">
-        <v>830</v>
+        <v>11350</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -999,10 +990,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="1">
-        <v>600</v>
+        <v>1350</v>
       </c>
       <c r="C8" s="1">
-        <v>1430</v>
+        <v>12700</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
@@ -1013,10 +1004,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="1">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="C9" s="1">
-        <v>2330</v>
+        <v>14500</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>16</v>
@@ -1027,10 +1018,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>1200</v>
+        <v>2250</v>
       </c>
       <c r="C10" s="1">
-        <v>3530</v>
+        <v>16750</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
@@ -1041,10 +1032,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>1600</v>
+        <v>2700</v>
       </c>
       <c r="C11" s="1">
-        <v>5130</v>
+        <v>19450</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
@@ -1055,10 +1046,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="1">
-        <v>2000</v>
+        <v>3150</v>
       </c>
       <c r="C12" s="1">
-        <v>7130</v>
+        <v>22600</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>19</v>
@@ -1069,10 +1060,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="C13" s="1">
-        <v>9530</v>
+        <v>26200</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>20</v>
@@ -1083,10 +1074,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>2800</v>
+        <v>4050</v>
       </c>
       <c r="C14" s="1">
-        <v>12330</v>
+        <v>30250</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>21</v>
@@ -1097,10 +1088,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="1">
-        <v>3200</v>
+        <v>4500</v>
       </c>
       <c r="C15" s="1">
-        <v>15530</v>
+        <v>34750</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>22</v>
@@ -1111,10 +1102,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>3600</v>
+        <v>4950</v>
       </c>
       <c r="C16" s="1">
-        <v>19130</v>
+        <v>39700</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>23</v>
@@ -1125,10 +1116,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>4000</v>
+        <v>5400</v>
       </c>
       <c r="C17" s="1">
-        <v>23130</v>
+        <v>45100</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>24</v>
@@ -1139,10 +1130,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="1">
-        <v>4400</v>
+        <v>5850</v>
       </c>
       <c r="C18" s="1">
-        <v>27530</v>
+        <v>50950</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>25</v>
@@ -1153,10 +1144,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="1">
-        <v>4800</v>
+        <v>6300</v>
       </c>
       <c r="C19" s="1">
-        <v>32330</v>
+        <v>57250</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>26</v>
@@ -1167,10 +1158,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="1">
-        <v>5200</v>
+        <v>6750</v>
       </c>
       <c r="C20" s="1">
-        <v>37530</v>
+        <v>64000</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>27</v>
@@ -1181,10 +1172,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="1">
-        <v>5600</v>
+        <v>7200</v>
       </c>
       <c r="C21" s="1">
-        <v>43130</v>
+        <v>71200</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>28</v>
@@ -1195,10 +1186,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="1">
-        <v>6000</v>
+        <v>7650</v>
       </c>
       <c r="C22" s="1">
-        <v>49130</v>
+        <v>78850</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>29</v>
@@ -1209,10 +1200,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="1">
-        <v>6400</v>
+        <v>8100</v>
       </c>
       <c r="C23" s="1">
-        <v>55530</v>
+        <v>86950</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>30</v>
@@ -1223,10 +1214,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="1">
-        <v>6800</v>
+        <v>8550</v>
       </c>
       <c r="C24" s="1">
-        <v>62330</v>
+        <v>95500</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>31</v>
@@ -1237,10 +1228,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="1">
-        <v>7200</v>
+        <v>9000</v>
       </c>
       <c r="C25" s="1">
-        <v>69530</v>
+        <v>104500</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>32</v>
@@ -1251,10 +1242,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="1">
-        <v>7600</v>
+        <v>9450</v>
       </c>
       <c r="C26" s="1">
-        <v>77130</v>
+        <v>113950</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>33</v>
@@ -1265,10 +1256,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="1">
-        <v>8000</v>
+        <v>9900</v>
       </c>
       <c r="C27" s="1">
-        <v>85130</v>
+        <v>123850</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>34</v>
@@ -1279,10 +1270,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="1">
-        <v>8400</v>
+        <v>10350</v>
       </c>
       <c r="C28" s="1">
-        <v>93530</v>
+        <v>134200</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>35</v>
@@ -1293,10 +1284,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="1">
-        <v>8800</v>
+        <v>10800</v>
       </c>
       <c r="C29" s="1">
-        <v>102330</v>
+        <v>145000</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>36</v>
@@ -1307,10 +1298,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="1">
-        <v>9200</v>
+        <v>11250</v>
       </c>
       <c r="C30" s="1">
-        <v>111530</v>
+        <v>156250</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>37</v>
@@ -1321,10 +1312,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="1">
-        <v>9600</v>
+        <v>11700</v>
       </c>
       <c r="C31" s="1">
-        <v>121130</v>
+        <v>167950</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>38</v>
@@ -1335,10 +1326,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="1">
-        <v>10000</v>
+        <v>12150</v>
       </c>
       <c r="C32" s="1">
-        <v>131130</v>
+        <v>180100</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>39</v>
@@ -1349,10 +1340,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="1">
-        <v>10400</v>
+        <v>12600</v>
       </c>
       <c r="C33" s="1">
-        <v>141530</v>
+        <v>192700</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>40</v>
@@ -1363,10 +1354,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="1">
-        <v>10800</v>
+        <v>13050</v>
       </c>
       <c r="C34" s="1">
-        <v>152330</v>
+        <v>205750</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>41</v>
@@ -1377,10 +1368,10 @@
         <v>31</v>
       </c>
       <c r="B35" s="1">
-        <v>11200</v>
+        <v>13500</v>
       </c>
       <c r="C35" s="1">
-        <v>163530</v>
+        <v>219250</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>42</v>
@@ -1391,10 +1382,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="1">
-        <v>11600</v>
+        <v>13950</v>
       </c>
       <c r="C36" s="1">
-        <v>175130</v>
+        <v>233200</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>43</v>
@@ -1405,10 +1396,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="1">
-        <v>12000</v>
+        <v>14400</v>
       </c>
       <c r="C37" s="1">
-        <v>187130</v>
+        <v>247600</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>44</v>
@@ -1419,10 +1410,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="1">
-        <v>12400</v>
+        <v>14850</v>
       </c>
       <c r="C38" s="1">
-        <v>199530</v>
+        <v>262450</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>45</v>
@@ -1433,10 +1424,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="1">
-        <v>12800</v>
+        <v>15300</v>
       </c>
       <c r="C39" s="1">
-        <v>212330</v>
+        <v>277750</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>46</v>
@@ -1447,10 +1438,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="1">
-        <v>13200</v>
+        <v>15750</v>
       </c>
       <c r="C40" s="1">
-        <v>225530</v>
+        <v>293500</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>47</v>
@@ -1461,10 +1452,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="1">
-        <v>13600</v>
+        <v>16200</v>
       </c>
       <c r="C41" s="1">
-        <v>239130</v>
+        <v>309700</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>48</v>
@@ -1475,10 +1466,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="1">
-        <v>14000</v>
+        <v>16650</v>
       </c>
       <c r="C42" s="1">
-        <v>253130</v>
+        <v>326350</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>49</v>
@@ -1489,10 +1480,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="1">
-        <v>14400</v>
+        <v>17100</v>
       </c>
       <c r="C43" s="1">
-        <v>267530</v>
+        <v>343450</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>50</v>
@@ -1503,10 +1494,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="1">
-        <v>14800</v>
+        <v>17550</v>
       </c>
       <c r="C44" s="1">
-        <v>282330</v>
+        <v>361000</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>51</v>
@@ -1517,10 +1508,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="1">
-        <v>15200</v>
+        <v>18000</v>
       </c>
       <c r="C45" s="1">
-        <v>297530</v>
+        <v>379000</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>52</v>
@@ -1531,10 +1522,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="1">
-        <v>15600</v>
+        <v>18450</v>
       </c>
       <c r="C46" s="1">
-        <v>313130</v>
+        <v>397450</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>53</v>
@@ -1545,10 +1536,10 @@
         <v>43</v>
       </c>
       <c r="B47" s="1">
-        <v>16000</v>
+        <v>18900</v>
       </c>
       <c r="C47" s="1">
-        <v>329130</v>
+        <v>416350</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>54</v>
@@ -1559,10 +1550,10 @@
         <v>44</v>
       </c>
       <c r="B48" s="1">
-        <v>16400</v>
+        <v>19350</v>
       </c>
       <c r="C48" s="1">
-        <v>345530</v>
+        <v>435700</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>55</v>
@@ -1573,10 +1564,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="1">
-        <v>16800</v>
+        <v>19800</v>
       </c>
       <c r="C49" s="1">
-        <v>362330</v>
+        <v>455500</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>56</v>
@@ -1587,10 +1578,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="1">
-        <v>17200</v>
+        <v>20250</v>
       </c>
       <c r="C50" s="1">
-        <v>379530</v>
+        <v>475750</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>57</v>
@@ -1601,10 +1592,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="1">
-        <v>17600</v>
+        <v>20700</v>
       </c>
       <c r="C51" s="1">
-        <v>397130</v>
+        <v>496450</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>58</v>
@@ -1615,10 +1606,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="1">
-        <v>18000</v>
+        <v>21150</v>
       </c>
       <c r="C52" s="1">
-        <v>415130</v>
+        <v>517600</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>59</v>
@@ -1629,10 +1620,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="1">
-        <v>18400</v>
+        <v>21600</v>
       </c>
       <c r="C53" s="1">
-        <v>433530</v>
+        <v>539200</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>60</v>
@@ -1643,10 +1634,10 @@
         <v>50</v>
       </c>
       <c r="B54" s="1">
-        <v>18800</v>
+        <v>22050</v>
       </c>
       <c r="C54" s="1">
-        <v>452330</v>
+        <v>561250</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>61</v>
@@ -1657,10 +1648,10 @@
         <v>51</v>
       </c>
       <c r="B55" s="1">
-        <v>19200</v>
+        <v>22500</v>
       </c>
       <c r="C55" s="1">
-        <v>471530</v>
+        <v>583750</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>62</v>
@@ -1671,10 +1662,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="1">
-        <v>19600</v>
+        <v>22950</v>
       </c>
       <c r="C56" s="1">
-        <v>491130</v>
+        <v>606700</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>63</v>
@@ -1685,10 +1676,10 @@
         <v>53</v>
       </c>
       <c r="B57" s="1">
-        <v>20000</v>
+        <v>23400</v>
       </c>
       <c r="C57" s="1">
-        <v>511130</v>
+        <v>630100</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>64</v>
@@ -1699,10 +1690,10 @@
         <v>54</v>
       </c>
       <c r="B58" s="1">
-        <v>20400</v>
+        <v>23850</v>
       </c>
       <c r="C58" s="1">
-        <v>531530</v>
+        <v>653950</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>65</v>
@@ -1713,10 +1704,10 @@
         <v>55</v>
       </c>
       <c r="B59" s="1">
-        <v>20800</v>
+        <v>24300</v>
       </c>
       <c r="C59" s="1">
-        <v>552330</v>
+        <v>678250</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>66</v>
@@ -1727,10 +1718,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="1">
-        <v>21200</v>
+        <v>24750</v>
       </c>
       <c r="C60" s="1">
-        <v>573530</v>
+        <v>703000</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>67</v>
@@ -1741,10 +1732,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="1">
-        <v>21600</v>
+        <v>25200</v>
       </c>
       <c r="C61" s="1">
-        <v>595130</v>
+        <v>728200</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>68</v>
@@ -1755,10 +1746,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="1">
-        <v>22000</v>
+        <v>25650</v>
       </c>
       <c r="C62" s="1">
-        <v>617130</v>
+        <v>753850</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>69</v>
@@ -1769,10 +1760,10 @@
         <v>59</v>
       </c>
       <c r="B63" s="1">
-        <v>22400</v>
+        <v>26100</v>
       </c>
       <c r="C63" s="1">
-        <v>639530</v>
+        <v>779950</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>70</v>
@@ -1783,10 +1774,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="1">
-        <v>22800</v>
+        <v>26550</v>
       </c>
       <c r="C64" s="1">
-        <v>662330</v>
+        <v>806500</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>71</v>
@@ -1797,10 +1788,10 @@
         <v>61</v>
       </c>
       <c r="B65" s="1">
-        <v>23200</v>
+        <v>27000</v>
       </c>
       <c r="C65" s="1">
-        <v>685530</v>
+        <v>833500</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>72</v>
@@ -1811,10 +1802,10 @@
         <v>62</v>
       </c>
       <c r="B66" s="1">
-        <v>23600</v>
+        <v>27450</v>
       </c>
       <c r="C66" s="1">
-        <v>709130</v>
+        <v>860950</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>73</v>
@@ -1825,10 +1816,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="1">
-        <v>24000</v>
+        <v>27900</v>
       </c>
       <c r="C67" s="1">
-        <v>733130</v>
+        <v>888850</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>74</v>
@@ -1839,10 +1830,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="1">
-        <v>24400</v>
+        <v>28350</v>
       </c>
       <c r="C68" s="1">
-        <v>757530</v>
+        <v>917200</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>75</v>
@@ -1853,10 +1844,10 @@
         <v>65</v>
       </c>
       <c r="B69" s="1">
-        <v>24800</v>
+        <v>28800</v>
       </c>
       <c r="C69" s="1">
-        <v>782330</v>
+        <v>946000</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>76</v>
@@ -1867,10 +1858,10 @@
         <v>66</v>
       </c>
       <c r="B70" s="1">
-        <v>25200</v>
+        <v>29250</v>
       </c>
       <c r="C70" s="1">
-        <v>807530</v>
+        <v>975250</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>77</v>
@@ -1881,10 +1872,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="1">
-        <v>25600</v>
+        <v>29700</v>
       </c>
       <c r="C71" s="1">
-        <v>833130</v>
+        <v>1004950</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>78</v>
@@ -1895,10 +1886,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="1">
-        <v>26000</v>
+        <v>30150</v>
       </c>
       <c r="C72" s="1">
-        <v>859130</v>
+        <v>1035100</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>79</v>
@@ -1909,10 +1900,10 @@
         <v>69</v>
       </c>
       <c r="B73" s="1">
-        <v>26400</v>
+        <v>30600</v>
       </c>
       <c r="C73" s="1">
-        <v>885530</v>
+        <v>1065700</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>80</v>
@@ -1923,10 +1914,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="1">
-        <v>26800</v>
+        <v>31050</v>
       </c>
       <c r="C74" s="1">
-        <v>912330</v>
+        <v>1096750</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>81</v>
@@ -1937,10 +1928,10 @@
         <v>71</v>
       </c>
       <c r="B75" s="1">
-        <v>27200</v>
+        <v>31500</v>
       </c>
       <c r="C75" s="1">
-        <v>939530</v>
+        <v>1128250</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>82</v>
@@ -1951,10 +1942,10 @@
         <v>72</v>
       </c>
       <c r="B76" s="1">
-        <v>27600</v>
+        <v>31950</v>
       </c>
       <c r="C76" s="1">
-        <v>967130</v>
+        <v>1160200</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>83</v>
@@ -1965,10 +1956,10 @@
         <v>73</v>
       </c>
       <c r="B77" s="1">
-        <v>28000</v>
+        <v>32400</v>
       </c>
       <c r="C77" s="1">
-        <v>995130</v>
+        <v>1192600</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>84</v>
@@ -1979,10 +1970,10 @@
         <v>74</v>
       </c>
       <c r="B78" s="1">
-        <v>28400</v>
+        <v>32850</v>
       </c>
       <c r="C78" s="1">
-        <v>1023530</v>
+        <v>1225450</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>85</v>
@@ -1993,10 +1984,10 @@
         <v>75</v>
       </c>
       <c r="B79" s="1">
-        <v>28800</v>
+        <v>33300</v>
       </c>
       <c r="C79" s="1">
-        <v>1052330</v>
+        <v>1258750</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>86</v>
@@ -2007,10 +1998,10 @@
         <v>76</v>
       </c>
       <c r="B80" s="1">
-        <v>29200</v>
+        <v>33750</v>
       </c>
       <c r="C80" s="1">
-        <v>1081530</v>
+        <v>1292500</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>87</v>
@@ -2021,10 +2012,10 @@
         <v>77</v>
       </c>
       <c r="B81" s="1">
-        <v>29600</v>
+        <v>34200</v>
       </c>
       <c r="C81" s="1">
-        <v>1111130</v>
+        <v>1326700</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>88</v>
@@ -2035,10 +2026,10 @@
         <v>78</v>
       </c>
       <c r="B82" s="1">
-        <v>30000</v>
+        <v>34650</v>
       </c>
       <c r="C82" s="1">
-        <v>1141130</v>
+        <v>1361350</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>89</v>
@@ -2049,10 +2040,10 @@
         <v>79</v>
       </c>
       <c r="B83" s="1">
-        <v>30400</v>
+        <v>35100</v>
       </c>
       <c r="C83" s="1">
-        <v>1171530</v>
+        <v>1396450</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>90</v>
@@ -2063,10 +2054,10 @@
         <v>80</v>
       </c>
       <c r="B84" s="1">
-        <v>30800</v>
+        <v>35550</v>
       </c>
       <c r="C84" s="1">
-        <v>1202330</v>
+        <v>1432000</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>91</v>
@@ -2077,10 +2068,10 @@
         <v>81</v>
       </c>
       <c r="B85" s="1">
-        <v>31200</v>
+        <v>36000</v>
       </c>
       <c r="C85" s="1">
-        <v>1233530</v>
+        <v>1468000</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>92</v>
@@ -2091,10 +2082,10 @@
         <v>82</v>
       </c>
       <c r="B86" s="1">
-        <v>31600</v>
+        <v>36450</v>
       </c>
       <c r="C86" s="1">
-        <v>1265130</v>
+        <v>1504450</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>93</v>
@@ -2105,10 +2096,10 @@
         <v>83</v>
       </c>
       <c r="B87" s="1">
-        <v>32000</v>
+        <v>36900</v>
       </c>
       <c r="C87" s="1">
-        <v>1297130</v>
+        <v>1541350</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>94</v>
@@ -2119,10 +2110,10 @@
         <v>84</v>
       </c>
       <c r="B88" s="1">
-        <v>32400</v>
+        <v>37350</v>
       </c>
       <c r="C88" s="1">
-        <v>1329530</v>
+        <v>1578700</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>95</v>
@@ -2133,10 +2124,10 @@
         <v>85</v>
       </c>
       <c r="B89" s="1">
-        <v>32800</v>
+        <v>37800</v>
       </c>
       <c r="C89" s="1">
-        <v>1362330</v>
+        <v>1616500</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>96</v>
@@ -2147,10 +2138,10 @@
         <v>86</v>
       </c>
       <c r="B90" s="1">
-        <v>33200</v>
+        <v>38250</v>
       </c>
       <c r="C90" s="1">
-        <v>1395530</v>
+        <v>1654750</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>97</v>
@@ -2161,10 +2152,10 @@
         <v>87</v>
       </c>
       <c r="B91" s="1">
-        <v>33600</v>
+        <v>38700</v>
       </c>
       <c r="C91" s="1">
-        <v>1429130</v>
+        <v>1693450</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>98</v>
@@ -2175,10 +2166,10 @@
         <v>88</v>
       </c>
       <c r="B92" s="1">
-        <v>34000</v>
+        <v>39150</v>
       </c>
       <c r="C92" s="1">
-        <v>1463130</v>
+        <v>1732600</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>99</v>
@@ -2189,10 +2180,10 @@
         <v>89</v>
       </c>
       <c r="B93" s="1">
-        <v>34400</v>
+        <v>39600</v>
       </c>
       <c r="C93" s="1">
-        <v>1497530</v>
+        <v>1772200</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>100</v>
@@ -2203,10 +2194,10 @@
         <v>90</v>
       </c>
       <c r="B94" s="1">
-        <v>34800</v>
+        <v>40050</v>
       </c>
       <c r="C94" s="1">
-        <v>1532330</v>
+        <v>1812250</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>101</v>
@@ -2217,10 +2208,10 @@
         <v>91</v>
       </c>
       <c r="B95" s="1">
-        <v>35200</v>
+        <v>40500</v>
       </c>
       <c r="C95" s="1">
-        <v>1567530</v>
+        <v>1852750</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>102</v>
@@ -2231,10 +2222,10 @@
         <v>92</v>
       </c>
       <c r="B96" s="1">
-        <v>35600</v>
+        <v>40950</v>
       </c>
       <c r="C96" s="1">
-        <v>1603130</v>
+        <v>1893700</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>103</v>
@@ -2245,10 +2236,10 @@
         <v>93</v>
       </c>
       <c r="B97" s="1">
-        <v>36000</v>
+        <v>41400</v>
       </c>
       <c r="C97" s="1">
-        <v>1639130</v>
+        <v>1935100</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>104</v>
@@ -2259,10 +2250,10 @@
         <v>94</v>
       </c>
       <c r="B98" s="1">
-        <v>36400</v>
+        <v>41850</v>
       </c>
       <c r="C98" s="1">
-        <v>1675530</v>
+        <v>1976950</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>105</v>
@@ -2273,10 +2264,10 @@
         <v>95</v>
       </c>
       <c r="B99" s="1">
-        <v>36800</v>
+        <v>42300</v>
       </c>
       <c r="C99" s="1">
-        <v>1712330</v>
+        <v>2019250</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>106</v>
@@ -2287,10 +2278,10 @@
         <v>96</v>
       </c>
       <c r="B100" s="1">
-        <v>37200</v>
+        <v>42750</v>
       </c>
       <c r="C100" s="1">
-        <v>1749530</v>
+        <v>2062000</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>107</v>
@@ -2301,10 +2292,10 @@
         <v>97</v>
       </c>
       <c r="B101" s="1">
-        <v>37600</v>
+        <v>43200</v>
       </c>
       <c r="C101" s="1">
-        <v>1787130</v>
+        <v>2105200</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>108</v>
@@ -2315,10 +2306,10 @@
         <v>98</v>
       </c>
       <c r="B102" s="1">
-        <v>38000</v>
+        <v>43650</v>
       </c>
       <c r="C102" s="1">
-        <v>1825130</v>
+        <v>2148850</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>109</v>
@@ -2329,10 +2320,10 @@
         <v>99</v>
       </c>
       <c r="B103" s="1">
-        <v>38400</v>
+        <v>44100</v>
       </c>
       <c r="C103" s="1">
-        <v>1863530</v>
+        <v>2192950</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>110</v>
@@ -2343,10 +2334,10 @@
         <v>100</v>
       </c>
       <c r="B104" s="1">
-        <v>38800</v>
+        <v>44550</v>
       </c>
       <c r="C104" s="1">
-        <v>1902330</v>
+        <v>2237500</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>111</v>
@@ -2357,10 +2348,10 @@
         <v>101</v>
       </c>
       <c r="B105" s="1">
-        <v>39200</v>
+        <v>45000</v>
       </c>
       <c r="C105" s="1">
-        <v>1941530</v>
+        <v>2282500</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>112</v>
@@ -2371,10 +2362,10 @@
         <v>102</v>
       </c>
       <c r="B106" s="1">
-        <v>39600</v>
+        <v>45450</v>
       </c>
       <c r="C106" s="1">
-        <v>1981130</v>
+        <v>2327950</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>113</v>
@@ -2385,10 +2376,10 @@
         <v>103</v>
       </c>
       <c r="B107" s="1">
-        <v>40000</v>
+        <v>45900</v>
       </c>
       <c r="C107" s="1">
-        <v>2021130</v>
+        <v>2373850</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>114</v>
@@ -2399,10 +2390,10 @@
         <v>104</v>
       </c>
       <c r="B108" s="1">
-        <v>40400</v>
+        <v>46350</v>
       </c>
       <c r="C108" s="1">
-        <v>2061530</v>
+        <v>2420200</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>115</v>
@@ -2413,10 +2404,10 @@
         <v>105</v>
       </c>
       <c r="B109" s="1">
-        <v>40800</v>
+        <v>46800</v>
       </c>
       <c r="C109" s="1">
-        <v>2102330</v>
+        <v>2467000</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>116</v>
@@ -2427,10 +2418,10 @@
         <v>106</v>
       </c>
       <c r="B110" s="1">
-        <v>41200</v>
+        <v>47250</v>
       </c>
       <c r="C110" s="1">
-        <v>2143530</v>
+        <v>2514250</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>117</v>
@@ -2441,10 +2432,10 @@
         <v>107</v>
       </c>
       <c r="B111" s="1">
-        <v>41600</v>
+        <v>47700</v>
       </c>
       <c r="C111" s="1">
-        <v>2185130</v>
+        <v>2561950</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>118</v>
@@ -2455,10 +2446,10 @@
         <v>108</v>
       </c>
       <c r="B112" s="1">
-        <v>42000</v>
+        <v>48150</v>
       </c>
       <c r="C112" s="1">
-        <v>2227130</v>
+        <v>2610100</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>119</v>
@@ -2469,10 +2460,10 @@
         <v>109</v>
       </c>
       <c r="B113" s="1">
-        <v>42400</v>
+        <v>48600</v>
       </c>
       <c r="C113" s="1">
-        <v>2269530</v>
+        <v>2658700</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>120</v>
@@ -2483,10 +2474,10 @@
         <v>110</v>
       </c>
       <c r="B114" s="1">
-        <v>42800</v>
+        <v>49050</v>
       </c>
       <c r="C114" s="1">
-        <v>2312330</v>
+        <v>2707750</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>121</v>
@@ -2497,10 +2488,10 @@
         <v>111</v>
       </c>
       <c r="B115" s="1">
-        <v>43200</v>
+        <v>49500</v>
       </c>
       <c r="C115" s="1">
-        <v>2355530</v>
+        <v>2757250</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>122</v>
@@ -2511,10 +2502,10 @@
         <v>112</v>
       </c>
       <c r="B116" s="1">
-        <v>43600</v>
+        <v>49950</v>
       </c>
       <c r="C116" s="1">
-        <v>2399130</v>
+        <v>2807200</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>123</v>
@@ -2525,10 +2516,10 @@
         <v>113</v>
       </c>
       <c r="B117" s="1">
-        <v>44000</v>
+        <v>50400</v>
       </c>
       <c r="C117" s="1">
-        <v>2443130</v>
+        <v>2857600</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>124</v>
@@ -2539,10 +2530,10 @@
         <v>114</v>
       </c>
       <c r="B118" s="1">
-        <v>44400</v>
+        <v>50850</v>
       </c>
       <c r="C118" s="1">
-        <v>2487530</v>
+        <v>2908450</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>125</v>
@@ -2553,10 +2544,10 @@
         <v>115</v>
       </c>
       <c r="B119" s="1">
-        <v>44800</v>
+        <v>51300</v>
       </c>
       <c r="C119" s="1">
-        <v>2532330</v>
+        <v>2959750</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>126</v>
@@ -2567,10 +2558,10 @@
         <v>116</v>
       </c>
       <c r="B120" s="1">
-        <v>45200</v>
+        <v>51750</v>
       </c>
       <c r="C120" s="1">
-        <v>2577530</v>
+        <v>3011500</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>127</v>
@@ -2581,10 +2572,10 @@
         <v>117</v>
       </c>
       <c r="B121" s="1">
-        <v>45600</v>
+        <v>52200</v>
       </c>
       <c r="C121" s="1">
-        <v>2623130</v>
+        <v>3063700</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>128</v>
@@ -2595,10 +2586,10 @@
         <v>118</v>
       </c>
       <c r="B122" s="1">
-        <v>46000</v>
+        <v>52650</v>
       </c>
       <c r="C122" s="1">
-        <v>2669130</v>
+        <v>3116350</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>129</v>
@@ -2609,10 +2600,10 @@
         <v>119</v>
       </c>
       <c r="B123" s="1">
-        <v>46400</v>
+        <v>53100</v>
       </c>
       <c r="C123" s="1">
-        <v>2715530</v>
+        <v>3169450</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>130</v>
@@ -2623,10 +2614,10 @@
         <v>120</v>
       </c>
       <c r="B124" s="1">
-        <v>46800</v>
+        <v>53550</v>
       </c>
       <c r="C124" s="1">
-        <v>2762330</v>
+        <v>3223000</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>131</v>
@@ -2637,10 +2628,10 @@
         <v>121</v>
       </c>
       <c r="B125" s="1">
-        <v>47200</v>
+        <v>54000</v>
       </c>
       <c r="C125" s="1">
-        <v>2809530</v>
+        <v>3277000</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>132</v>
@@ -2651,10 +2642,10 @@
         <v>122</v>
       </c>
       <c r="B126" s="1">
-        <v>47600</v>
+        <v>54450</v>
       </c>
       <c r="C126" s="1">
-        <v>2857130</v>
+        <v>3331450</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>133</v>
@@ -2665,10 +2656,10 @@
         <v>123</v>
       </c>
       <c r="B127" s="1">
-        <v>48000</v>
+        <v>54900</v>
       </c>
       <c r="C127" s="1">
-        <v>2905130</v>
+        <v>3386350</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>134</v>
@@ -2679,10 +2670,10 @@
         <v>124</v>
       </c>
       <c r="B128" s="1">
-        <v>48400</v>
+        <v>55350</v>
       </c>
       <c r="C128" s="1">
-        <v>2953530</v>
+        <v>3441700</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>135</v>
@@ -2693,10 +2684,10 @@
         <v>125</v>
       </c>
       <c r="B129" s="1">
-        <v>48800</v>
+        <v>55800</v>
       </c>
       <c r="C129" s="1">
-        <v>3002330</v>
+        <v>3497500</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>136</v>
@@ -2707,10 +2698,10 @@
         <v>126</v>
       </c>
       <c r="B130" s="1">
-        <v>49200</v>
+        <v>56250</v>
       </c>
       <c r="C130" s="1">
-        <v>3051530</v>
+        <v>3553750</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>137</v>
@@ -2721,10 +2712,10 @@
         <v>127</v>
       </c>
       <c r="B131" s="1">
-        <v>49600</v>
+        <v>56700</v>
       </c>
       <c r="C131" s="1">
-        <v>3101130</v>
+        <v>3610450</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>138</v>
@@ -2735,10 +2726,10 @@
         <v>128</v>
       </c>
       <c r="B132" s="1">
-        <v>50000</v>
+        <v>57150</v>
       </c>
       <c r="C132" s="1">
-        <v>3151130</v>
+        <v>3667600</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>139</v>
@@ -2749,10 +2740,10 @@
         <v>129</v>
       </c>
       <c r="B133" s="1">
-        <v>50400</v>
+        <v>57600</v>
       </c>
       <c r="C133" s="1">
-        <v>3201530</v>
+        <v>3725200</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>140</v>
@@ -2763,10 +2754,10 @@
         <v>130</v>
       </c>
       <c r="B134" s="1">
-        <v>50800</v>
+        <v>58050</v>
       </c>
       <c r="C134" s="1">
-        <v>3252330</v>
+        <v>3783250</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>141</v>
@@ -2777,10 +2768,10 @@
         <v>131</v>
       </c>
       <c r="B135" s="1">
-        <v>51200</v>
+        <v>58500</v>
       </c>
       <c r="C135" s="1">
-        <v>3303530</v>
+        <v>3841750</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>142</v>
@@ -2791,10 +2782,10 @@
         <v>132</v>
       </c>
       <c r="B136" s="1">
-        <v>51600</v>
+        <v>58950</v>
       </c>
       <c r="C136" s="1">
-        <v>3355130</v>
+        <v>3900700</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>143</v>
@@ -2805,10 +2796,10 @@
         <v>133</v>
       </c>
       <c r="B137" s="1">
-        <v>52000</v>
+        <v>59400</v>
       </c>
       <c r="C137" s="1">
-        <v>3407130</v>
+        <v>3960100</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>144</v>
@@ -2819,10 +2810,10 @@
         <v>134</v>
       </c>
       <c r="B138" s="1">
-        <v>52400</v>
+        <v>59850</v>
       </c>
       <c r="C138" s="1">
-        <v>3459530</v>
+        <v>4019950</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>145</v>
@@ -2833,10 +2824,10 @@
         <v>135</v>
       </c>
       <c r="B139" s="1">
-        <v>52800</v>
+        <v>60300</v>
       </c>
       <c r="C139" s="1">
-        <v>3512330</v>
+        <v>4080250</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>146</v>
@@ -2847,10 +2838,10 @@
         <v>136</v>
       </c>
       <c r="B140" s="1">
-        <v>53200</v>
+        <v>60750</v>
       </c>
       <c r="C140" s="1">
-        <v>3565530</v>
+        <v>4141000</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>147</v>
@@ -2861,10 +2852,10 @@
         <v>137</v>
       </c>
       <c r="B141" s="1">
-        <v>53600</v>
+        <v>61200</v>
       </c>
       <c r="C141" s="1">
-        <v>3619130</v>
+        <v>4202200</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>148</v>
@@ -2875,10 +2866,10 @@
         <v>138</v>
       </c>
       <c r="B142" s="1">
-        <v>54000</v>
+        <v>61650</v>
       </c>
       <c r="C142" s="1">
-        <v>3673130</v>
+        <v>4263850</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>149</v>
@@ -2889,10 +2880,10 @@
         <v>139</v>
       </c>
       <c r="B143" s="1">
-        <v>54400</v>
+        <v>62100</v>
       </c>
       <c r="C143" s="1">
-        <v>3727530</v>
+        <v>4325950</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>150</v>
@@ -2903,10 +2894,10 @@
         <v>140</v>
       </c>
       <c r="B144" s="1">
-        <v>54800</v>
+        <v>62550</v>
       </c>
       <c r="C144" s="1">
-        <v>3782330</v>
+        <v>4388500</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>151</v>
@@ -2917,10 +2908,10 @@
         <v>141</v>
       </c>
       <c r="B145" s="1">
-        <v>55200</v>
+        <v>63000</v>
       </c>
       <c r="C145" s="1">
-        <v>3837530</v>
+        <v>4451500</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>152</v>
@@ -2931,10 +2922,10 @@
         <v>142</v>
       </c>
       <c r="B146" s="1">
-        <v>55600</v>
+        <v>63450</v>
       </c>
       <c r="C146" s="1">
-        <v>3893130</v>
+        <v>4514950</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>153</v>
@@ -2945,10 +2936,10 @@
         <v>143</v>
       </c>
       <c r="B147" s="1">
-        <v>56000</v>
+        <v>63900</v>
       </c>
       <c r="C147" s="1">
-        <v>3949130</v>
+        <v>4578850</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>154</v>
@@ -2959,10 +2950,10 @@
         <v>144</v>
       </c>
       <c r="B148" s="1">
-        <v>56400</v>
+        <v>64350</v>
       </c>
       <c r="C148" s="1">
-        <v>4005530</v>
+        <v>4643200</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>155</v>
@@ -2973,10 +2964,10 @@
         <v>145</v>
       </c>
       <c r="B149" s="1">
-        <v>56800</v>
+        <v>64800</v>
       </c>
       <c r="C149" s="1">
-        <v>4062330</v>
+        <v>4708000</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>156</v>
@@ -2987,10 +2978,10 @@
         <v>146</v>
       </c>
       <c r="B150" s="1">
-        <v>57200</v>
+        <v>65250</v>
       </c>
       <c r="C150" s="1">
-        <v>4119530</v>
+        <v>4773250</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>157</v>
@@ -3001,10 +2992,10 @@
         <v>147</v>
       </c>
       <c r="B151" s="1">
-        <v>57600</v>
+        <v>65700</v>
       </c>
       <c r="C151" s="1">
-        <v>4177130</v>
+        <v>4838950</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>158</v>
@@ -3015,10 +3006,10 @@
         <v>148</v>
       </c>
       <c r="B152" s="1">
-        <v>58000</v>
+        <v>66150</v>
       </c>
       <c r="C152" s="1">
-        <v>4235130</v>
+        <v>4905100</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>159</v>
@@ -3029,10 +3020,10 @@
         <v>149</v>
       </c>
       <c r="B153" s="1">
-        <v>58400</v>
+        <v>66600</v>
       </c>
       <c r="C153" s="1">
-        <v>4293530</v>
+        <v>4971700</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>160</v>
@@ -3043,10 +3034,10 @@
         <v>150</v>
       </c>
       <c r="B154" s="1">
-        <v>58800</v>
+        <v>67050</v>
       </c>
       <c r="C154" s="1">
-        <v>4352330</v>
+        <v>5038750</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>161</v>
@@ -3057,10 +3048,10 @@
         <v>151</v>
       </c>
       <c r="B155" s="1">
-        <v>59200</v>
+        <v>67500</v>
       </c>
       <c r="C155" s="1">
-        <v>4411530</v>
+        <v>5106250</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>162</v>
@@ -3071,10 +3062,10 @@
         <v>152</v>
       </c>
       <c r="B156" s="1">
-        <v>59600</v>
+        <v>67950</v>
       </c>
       <c r="C156" s="1">
-        <v>4471130</v>
+        <v>5174200</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>163</v>
@@ -3085,10 +3076,10 @@
         <v>153</v>
       </c>
       <c r="B157" s="1">
-        <v>60000</v>
+        <v>68400</v>
       </c>
       <c r="C157" s="1">
-        <v>4531130</v>
+        <v>5242600</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>164</v>
@@ -3099,10 +3090,10 @@
         <v>154</v>
       </c>
       <c r="B158" s="1">
-        <v>60400</v>
+        <v>68850</v>
       </c>
       <c r="C158" s="1">
-        <v>4591530</v>
+        <v>5311450</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>165</v>
@@ -3113,10 +3104,10 @@
         <v>155</v>
       </c>
       <c r="B159" s="1">
-        <v>60800</v>
+        <v>69300</v>
       </c>
       <c r="C159" s="1">
-        <v>4652330</v>
+        <v>5380750</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>166</v>
@@ -3127,10 +3118,10 @@
         <v>156</v>
       </c>
       <c r="B160" s="1">
-        <v>61200</v>
+        <v>69750</v>
       </c>
       <c r="C160" s="1">
-        <v>4713530</v>
+        <v>5450500</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>167</v>
@@ -3141,10 +3132,10 @@
         <v>157</v>
       </c>
       <c r="B161" s="1">
-        <v>61600</v>
+        <v>70200</v>
       </c>
       <c r="C161" s="1">
-        <v>4775130</v>
+        <v>5520700</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>168</v>
@@ -3155,10 +3146,10 @@
         <v>158</v>
       </c>
       <c r="B162" s="1">
-        <v>62000</v>
+        <v>70650</v>
       </c>
       <c r="C162" s="1">
-        <v>4837130</v>
+        <v>5591350</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>169</v>
@@ -3169,10 +3160,10 @@
         <v>159</v>
       </c>
       <c r="B163" s="1">
-        <v>62400</v>
+        <v>71100</v>
       </c>
       <c r="C163" s="1">
-        <v>4899530</v>
+        <v>5662450</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>170</v>
@@ -3186,7 +3177,7 @@
         <v>-1</v>
       </c>
       <c r="C164" s="1">
-        <v>4899530</v>
+        <v>5662450</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>171</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
@@ -5,20 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098EC3CE-315C-4E4A-B3FE-06322FA62054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3F826A-32A0-44C1-9943-6C85BFBDAB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -73,484 +82,484 @@
     <t>MAP&lt;INT:LONG&gt;_C_S</t>
   </si>
   <si>
-    <t>9101:50</t>
-  </si>
-  <si>
-    <t>9101:100</t>
-  </si>
-  <si>
-    <t>9101:150</t>
-  </si>
-  <si>
-    <t>9101:200</t>
-  </si>
-  <si>
-    <t>9101:250</t>
-  </si>
-  <si>
-    <t>9101:300</t>
-  </si>
-  <si>
-    <t>9101:350</t>
-  </si>
-  <si>
-    <t>9101:400</t>
-  </si>
-  <si>
-    <t>9101:450</t>
-  </si>
-  <si>
-    <t>9101:500</t>
-  </si>
-  <si>
-    <t>9101:550</t>
-  </si>
-  <si>
-    <t>9101:600</t>
-  </si>
-  <si>
-    <t>9101:650</t>
-  </si>
-  <si>
-    <t>9101:700</t>
-  </si>
-  <si>
-    <t>9101:750</t>
-  </si>
-  <si>
-    <t>9101:800</t>
-  </si>
-  <si>
-    <t>9101:850</t>
-  </si>
-  <si>
-    <t>9101:900</t>
-  </si>
-  <si>
-    <t>9101:950</t>
-  </si>
-  <si>
-    <t>9101:1000</t>
-  </si>
-  <si>
-    <t>9101:1050</t>
-  </si>
-  <si>
-    <t>9101:1100</t>
-  </si>
-  <si>
-    <t>9101:1150</t>
-  </si>
-  <si>
-    <t>9101:1200</t>
-  </si>
-  <si>
-    <t>9101:1250</t>
-  </si>
-  <si>
-    <t>9101:1300</t>
-  </si>
-  <si>
-    <t>9101:1350</t>
-  </si>
-  <si>
-    <t>9101:1400</t>
-  </si>
-  <si>
-    <t>9101:1450</t>
-  </si>
-  <si>
-    <t>9101:1500</t>
-  </si>
-  <si>
-    <t>9101:1550</t>
-  </si>
-  <si>
-    <t>9101:1600</t>
-  </si>
-  <si>
-    <t>9101:1650</t>
-  </si>
-  <si>
-    <t>9101:1700</t>
-  </si>
-  <si>
-    <t>9101:1750</t>
-  </si>
-  <si>
-    <t>9101:1800</t>
-  </si>
-  <si>
-    <t>9101:1850</t>
-  </si>
-  <si>
-    <t>9101:1900</t>
-  </si>
-  <si>
-    <t>9101:1950</t>
-  </si>
-  <si>
-    <t>9101:2000</t>
-  </si>
-  <si>
-    <t>9101:2050</t>
-  </si>
-  <si>
-    <t>9101:2100</t>
-  </si>
-  <si>
-    <t>9101:2150</t>
-  </si>
-  <si>
-    <t>9101:2200</t>
-  </si>
-  <si>
-    <t>9101:2250</t>
-  </si>
-  <si>
-    <t>9101:2300</t>
-  </si>
-  <si>
-    <t>9101:2350</t>
-  </si>
-  <si>
-    <t>9101:2400</t>
-  </si>
-  <si>
-    <t>9101:2450</t>
-  </si>
-  <si>
-    <t>9101:2500</t>
-  </si>
-  <si>
-    <t>9101:2550</t>
-  </si>
-  <si>
-    <t>9101:2600</t>
-  </si>
-  <si>
-    <t>9101:2650</t>
-  </si>
-  <si>
-    <t>9101:2700</t>
-  </si>
-  <si>
-    <t>9101:2750</t>
-  </si>
-  <si>
-    <t>9101:2800</t>
-  </si>
-  <si>
-    <t>9101:2850</t>
-  </si>
-  <si>
-    <t>9101:2900</t>
-  </si>
-  <si>
-    <t>9101:2950</t>
-  </si>
-  <si>
-    <t>9101:3000</t>
-  </si>
-  <si>
-    <t>9101:3050</t>
-  </si>
-  <si>
-    <t>9101:3100</t>
-  </si>
-  <si>
-    <t>9101:3150</t>
-  </si>
-  <si>
-    <t>9101:3200</t>
-  </si>
-  <si>
-    <t>9101:3250</t>
-  </si>
-  <si>
-    <t>9101:3300</t>
-  </si>
-  <si>
-    <t>9101:3350</t>
-  </si>
-  <si>
-    <t>9101:3400</t>
-  </si>
-  <si>
-    <t>9101:3450</t>
-  </si>
-  <si>
-    <t>9101:3500</t>
-  </si>
-  <si>
-    <t>9101:3550</t>
-  </si>
-  <si>
-    <t>9101:3600</t>
-  </si>
-  <si>
-    <t>9101:3650</t>
-  </si>
-  <si>
-    <t>9101:3700</t>
-  </si>
-  <si>
-    <t>9101:3750</t>
-  </si>
-  <si>
-    <t>9101:3800</t>
-  </si>
-  <si>
-    <t>9101:3850</t>
-  </si>
-  <si>
-    <t>9101:3900</t>
-  </si>
-  <si>
-    <t>9101:3950</t>
-  </si>
-  <si>
-    <t>9101:4000</t>
-  </si>
-  <si>
-    <t>9101:4050</t>
-  </si>
-  <si>
-    <t>9101:4100</t>
-  </si>
-  <si>
-    <t>9101:4150</t>
-  </si>
-  <si>
-    <t>9101:4200</t>
-  </si>
-  <si>
-    <t>9101:4250</t>
-  </si>
-  <si>
-    <t>9101:4300</t>
-  </si>
-  <si>
-    <t>9101:4350</t>
-  </si>
-  <si>
-    <t>9101:4400</t>
-  </si>
-  <si>
-    <t>9101:4450</t>
-  </si>
-  <si>
-    <t>9101:4500</t>
-  </si>
-  <si>
-    <t>9101:4550</t>
-  </si>
-  <si>
-    <t>9101:4600</t>
-  </si>
-  <si>
-    <t>9101:4650</t>
-  </si>
-  <si>
-    <t>9101:4700</t>
-  </si>
-  <si>
-    <t>9101:4750</t>
-  </si>
-  <si>
-    <t>9101:4800</t>
-  </si>
-  <si>
-    <t>9101:4850</t>
-  </si>
-  <si>
-    <t>9101:4900</t>
-  </si>
-  <si>
-    <t>9101:4950</t>
-  </si>
-  <si>
-    <t>9101:5000</t>
-  </si>
-  <si>
-    <t>9101:5050</t>
-  </si>
-  <si>
-    <t>9101:5100</t>
-  </si>
-  <si>
-    <t>9101:5150</t>
-  </si>
-  <si>
-    <t>9101:5200</t>
-  </si>
-  <si>
-    <t>9101:5250</t>
-  </si>
-  <si>
-    <t>9101:5300</t>
-  </si>
-  <si>
-    <t>9101:5350</t>
-  </si>
-  <si>
-    <t>9101:5400</t>
-  </si>
-  <si>
-    <t>9101:5450</t>
-  </si>
-  <si>
-    <t>9101:5500</t>
-  </si>
-  <si>
-    <t>9101:5550</t>
-  </si>
-  <si>
-    <t>9101:5600</t>
-  </si>
-  <si>
-    <t>9101:5650</t>
-  </si>
-  <si>
-    <t>9101:5700</t>
-  </si>
-  <si>
-    <t>9101:5750</t>
-  </si>
-  <si>
-    <t>9101:5800</t>
-  </si>
-  <si>
-    <t>9101:5850</t>
-  </si>
-  <si>
-    <t>9101:5900</t>
-  </si>
-  <si>
-    <t>9101:5950</t>
-  </si>
-  <si>
-    <t>9101:6000</t>
-  </si>
-  <si>
-    <t>9101:6050</t>
-  </si>
-  <si>
-    <t>9101:6100</t>
-  </si>
-  <si>
-    <t>9101:6150</t>
-  </si>
-  <si>
-    <t>9101:6200</t>
-  </si>
-  <si>
-    <t>9101:6250</t>
-  </si>
-  <si>
-    <t>9101:6300</t>
-  </si>
-  <si>
-    <t>9101:6350</t>
-  </si>
-  <si>
-    <t>9101:6400</t>
-  </si>
-  <si>
-    <t>9101:6450</t>
-  </si>
-  <si>
-    <t>9101:6500</t>
-  </si>
-  <si>
-    <t>9101:6550</t>
-  </si>
-  <si>
-    <t>9101:6600</t>
-  </si>
-  <si>
-    <t>9101:6650</t>
-  </si>
-  <si>
-    <t>9101:6700</t>
-  </si>
-  <si>
-    <t>9101:6750</t>
-  </si>
-  <si>
-    <t>9101:6800</t>
-  </si>
-  <si>
-    <t>9101:6850</t>
-  </si>
-  <si>
-    <t>9101:6900</t>
-  </si>
-  <si>
-    <t>9101:6950</t>
-  </si>
-  <si>
-    <t>9101:7000</t>
-  </si>
-  <si>
-    <t>9101:7050</t>
-  </si>
-  <si>
-    <t>9101:7100</t>
-  </si>
-  <si>
-    <t>9101:7150</t>
-  </si>
-  <si>
-    <t>9101:7200</t>
-  </si>
-  <si>
-    <t>9101:7250</t>
-  </si>
-  <si>
-    <t>9101:7300</t>
-  </si>
-  <si>
-    <t>9101:7350</t>
-  </si>
-  <si>
-    <t>9101:7400</t>
-  </si>
-  <si>
-    <t>9101:7450</t>
-  </si>
-  <si>
-    <t>9101:7500</t>
-  </si>
-  <si>
-    <t>9101:7550</t>
-  </si>
-  <si>
-    <t>9101:7600</t>
-  </si>
-  <si>
-    <t>9101:7650</t>
-  </si>
-  <si>
-    <t>9101:7700</t>
-  </si>
-  <si>
-    <t>9101:7750</t>
-  </si>
-  <si>
-    <t>9101:7800</t>
-  </si>
-  <si>
-    <t>9101:7850</t>
-  </si>
-  <si>
-    <t>9101:7900</t>
-  </si>
-  <si>
-    <t>9101:7950</t>
-  </si>
-  <si>
-    <t>9101:8000</t>
+    <t>3010101:1_3020101:1_3030101:20_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:2_3020101:2_3030101:40_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:3_3020101:3_3030101:60_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:4_3020101:4_3030101:80_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:5_3020101:5_3030101:104_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:7_3020101:7_3030101:137_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:9_3020101:9_3030101:180_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:12_3020101:12_3030101:235_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:15_3020101:15_3030101:302_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:20_3020101:20_3030101:401_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:29_3020101:29_3030101:581_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:43_3020101:43_3030101:866_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:64_3020101:64_3030101:1283_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:93_3020101:93_3030101:1859_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:131_3020101:131_3030101:2620_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:180_3020101:180_3030101:3593_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:241_3020101:241_3030101:4805_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:315_3020101:315_3030101:6282_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:403_3020101:403_3030101:8051_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:507_3020101:507_3030101:10139_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:629_3020101:629_3030101:12572_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:769_3020101:769_3030101:15377_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:929_3020101:929_3030101:18581_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:1110_3020101:1110_3030101:22210_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:1314_3020101:1314_3030101:26291_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:1542_3020101:1542_3030101:30851_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:1795_3020101:1795_3030101:35916_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:2075_3020101:2075_3030101:41513_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:2383_3020101:2383_3030101:47669_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:2720_3020101:2720_3030101:54410_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:3088_3020101:3088_3030101:61763_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:3488_3020101:3488_3030101:69755_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:3921_3020101:3921_3030101:78412_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:4388_3020101:4388_3030101:87761_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:4891_3020101:4891_3030101:97829_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:5432_3020101:5432_3030101:108642_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:6011_3020101:6011_3030101:120227_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:6630_3020101:6630_3030101:132611_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:7290_3020101:7290_3030101:145820_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:7993_3020101:7993_3030101:159881_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:8740_3020101:8740_3030101:174821_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:9532_3020101:9532_3030101:190666_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:10371_3020101:10371_3030101:207443_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:11258_3020101:11258_3030101:225179_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:12194_3020101:12194_3030101:243900_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:13181_3020101:13181_3030101:263633_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:14220_3020101:14220_3030101:284406_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:15313_3020101:15313_3030101:306273_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:16463_3020101:16463_3030101:329273_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:17672_3020101:17672_3030101:353446_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:18942_3020101:18942_3030101:378846_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:20275_3020101:20275_3030101:405513_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:21674_3020101:21674_3030101:433500_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:23142_3020101:23142_3030101:462860_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:24681_3020101:24681_3030101:493647_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:26294_3020101:26294_3030101:525914_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:27984_3020101:27984_3030101:559714_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:29753_3020101:29753_3030101:595101_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:31605_3020101:31605_3030101:632141_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:33542_3020101:33542_3030101:670888_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:35568_3020101:35568_3030101:711408_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:37686_3020101:37686_3030101:753768_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:39899_3020101:39899_3030101:798021_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:42210_3020101:42210_3030101:844234_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:44623_3020101:44623_3030101:892487_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:47141_3020101:47141_3030101:942847_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:49768_3020101:49768_3030101:995380_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:52507_3020101:52507_3030101:1050167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:55363_3020101:55363_3030101:1107287_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:58340_3020101:58340_3030101:1166820_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:61441_3020101:61441_3030101:1228847_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:64671_3020101:64671_3030101:1293447_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:68034_3020101:68034_3030101:1360700_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:71534_3020101:71534_3030101:1430700_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:75176_3020101:75176_3030101:1503540_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:78965_3020101:78965_3030101:1579313_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:82905_3020101:82905_3030101:1658113_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:87001_3020101:87001_3030101:1740033_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:91258_3020101:91258_3030101:1825180_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:95682_3020101:95682_3030101:1913660_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:100278_3020101:100278_3030101:2005580_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:105051_3020101:105051_3030101:2101047_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:110007_3020101:110007_3030101:2200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:115007_3020101:115007_3030101:2300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:120007_3020101:120007_3030101:2400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:125007_3020101:125007_3030101:2500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:130007_3020101:130007_3030101:2600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:135007_3020101:135007_3030101:2700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:140007_3020101:140007_3030101:2800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:145007_3020101:145007_3030101:2900167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:150007_3020101:150007_3030101:3000167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:155007_3020101:155007_3030101:3100167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:160007_3020101:160007_3030101:3200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:165007_3020101:165007_3030101:3300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:170007_3020101:170007_3030101:3400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:175007_3020101:175007_3030101:3500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:180007_3020101:180007_3030101:3600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:185007_3020101:185007_3030101:3700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:190007_3020101:190007_3030101:3800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:195007_3020101:195007_3030101:3900167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:200007_3020101:200007_3030101:4000167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:205007_3020101:205007_3030101:4100167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:210007_3020101:210007_3030101:4200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:215007_3020101:215007_3030101:4300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:220007_3020101:220007_3030101:4400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:225007_3020101:225007_3030101:4500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:230007_3020101:230007_3030101:4600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:235007_3020101:235007_3030101:4700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:240007_3020101:240007_3030101:4800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:245007_3020101:245007_3030101:4900167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:250007_3020101:250007_3030101:5000167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:255007_3020101:255007_3030101:5100167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:260007_3020101:260007_3030101:5200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:265007_3020101:265007_3030101:5300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:270007_3020101:270007_3030101:5400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:275007_3020101:275007_3030101:5500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:280007_3020101:280007_3030101:5600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:285007_3020101:285007_3030101:5700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:290007_3020101:290007_3030101:5800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:295007_3020101:295007_3030101:5900167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:300007_3020101:300007_3030101:6000167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:305007_3020101:305007_3030101:6100167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:310007_3020101:310007_3030101:6200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:315007_3020101:315007_3030101:6300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:320007_3020101:320007_3030101:6400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:325007_3020101:325007_3030101:6500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:330007_3020101:330007_3030101:6600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:335007_3020101:335007_3030101:6700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:340007_3020101:340007_3030101:6800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:345007_3020101:345007_3030101:6900167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:350007_3020101:350007_3030101:7000167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:355007_3020101:355007_3030101:7100167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:360007_3020101:360007_3030101:7200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:365007_3020101:365007_3030101:7300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:370007_3020101:370007_3030101:7400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:375007_3020101:375007_3030101:7500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:380007_3020101:380007_3030101:7600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:385007_3020101:385007_3030101:7700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:390007_3020101:390007_3030101:7800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:395007_3020101:395007_3030101:7900167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:400007_3020101:400007_3030101:8000167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:405007_3020101:405007_3030101:8100167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:410007_3020101:410007_3030101:8200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:415007_3020101:415007_3030101:8300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:420007_3020101:420007_3030101:8400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:425007_3020101:425007_3030101:8500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:430007_3020101:430007_3030101:8600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:435007_3020101:435007_3030101:8700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:440007_3020101:440007_3030101:8800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:445007_3020101:445007_3030101:8900167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:450007_3020101:450007_3030101:9000167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:455007_3020101:455007_3030101:9100167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:460007_3020101:460007_3030101:9200167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:465007_3020101:465007_3030101:9300167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:470007_3020101:470007_3030101:9400167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:475007_3020101:475007_3030101:9500167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:480007_3020101:480007_3030101:9600167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:485007_3020101:485007_3030101:9700167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:490007_3020101:490007_3030101:9800167_9101:3</t>
+  </si>
+  <si>
+    <t>3010101:495007_3020101:495007_3030101:9900167_9101:3</t>
   </si>
 </sst>
 </file>
@@ -890,7 +899,7 @@
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -948,10 +957,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>10000</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1">
-        <v>10000</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -962,10 +971,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="C6" s="1">
-        <v>10450</v>
+        <v>330</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>13</v>
@@ -976,10 +985,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="C7" s="1">
-        <v>11350</v>
+        <v>830</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -990,10 +999,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="1">
-        <v>1350</v>
+        <v>600</v>
       </c>
       <c r="C8" s="1">
-        <v>12700</v>
+        <v>1430</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
@@ -1004,10 +1013,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="1">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="C9" s="1">
-        <v>14500</v>
+        <v>2330</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>16</v>
@@ -1018,10 +1027,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>2250</v>
+        <v>1200</v>
       </c>
       <c r="C10" s="1">
-        <v>16750</v>
+        <v>3530</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
@@ -1032,10 +1041,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>2700</v>
+        <v>1600</v>
       </c>
       <c r="C11" s="1">
-        <v>19450</v>
+        <v>5130</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
@@ -1046,10 +1055,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="1">
-        <v>3150</v>
+        <v>2000</v>
       </c>
       <c r="C12" s="1">
-        <v>22600</v>
+        <v>7130</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>19</v>
@@ -1060,10 +1069,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="C13" s="1">
-        <v>26200</v>
+        <v>9530</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>20</v>
@@ -1074,10 +1083,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>4050</v>
+        <v>2800</v>
       </c>
       <c r="C14" s="1">
-        <v>30250</v>
+        <v>12330</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>21</v>
@@ -1088,10 +1097,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="1">
-        <v>4500</v>
+        <v>3200</v>
       </c>
       <c r="C15" s="1">
-        <v>34750</v>
+        <v>15530</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>22</v>
@@ -1102,10 +1111,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>4950</v>
+        <v>3600</v>
       </c>
       <c r="C16" s="1">
-        <v>39700</v>
+        <v>19130</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>23</v>
@@ -1116,10 +1125,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>5400</v>
+        <v>4000</v>
       </c>
       <c r="C17" s="1">
-        <v>45100</v>
+        <v>23130</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>24</v>
@@ -1130,10 +1139,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="1">
-        <v>5850</v>
+        <v>4400</v>
       </c>
       <c r="C18" s="1">
-        <v>50950</v>
+        <v>27530</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>25</v>
@@ -1144,10 +1153,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="1">
-        <v>6300</v>
+        <v>4800</v>
       </c>
       <c r="C19" s="1">
-        <v>57250</v>
+        <v>32330</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>26</v>
@@ -1158,10 +1167,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="1">
-        <v>6750</v>
+        <v>5200</v>
       </c>
       <c r="C20" s="1">
-        <v>64000</v>
+        <v>37530</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>27</v>
@@ -1172,10 +1181,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="1">
-        <v>7200</v>
+        <v>5600</v>
       </c>
       <c r="C21" s="1">
-        <v>71200</v>
+        <v>43130</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>28</v>
@@ -1186,10 +1195,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="1">
-        <v>7650</v>
+        <v>6000</v>
       </c>
       <c r="C22" s="1">
-        <v>78850</v>
+        <v>49130</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>29</v>
@@ -1200,10 +1209,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="1">
-        <v>8100</v>
+        <v>6400</v>
       </c>
       <c r="C23" s="1">
-        <v>86950</v>
+        <v>55530</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>30</v>
@@ -1214,10 +1223,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="1">
-        <v>8550</v>
+        <v>6800</v>
       </c>
       <c r="C24" s="1">
-        <v>95500</v>
+        <v>62330</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>31</v>
@@ -1228,10 +1237,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="1">
-        <v>9000</v>
+        <v>7200</v>
       </c>
       <c r="C25" s="1">
-        <v>104500</v>
+        <v>69530</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>32</v>
@@ -1242,10 +1251,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="1">
-        <v>9450</v>
+        <v>7600</v>
       </c>
       <c r="C26" s="1">
-        <v>113950</v>
+        <v>77130</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>33</v>
@@ -1256,10 +1265,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="1">
-        <v>9900</v>
+        <v>8000</v>
       </c>
       <c r="C27" s="1">
-        <v>123850</v>
+        <v>85130</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>34</v>
@@ -1270,10 +1279,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="1">
-        <v>10350</v>
+        <v>8400</v>
       </c>
       <c r="C28" s="1">
-        <v>134200</v>
+        <v>93530</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>35</v>
@@ -1284,10 +1293,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="1">
-        <v>10800</v>
+        <v>8800</v>
       </c>
       <c r="C29" s="1">
-        <v>145000</v>
+        <v>102330</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>36</v>
@@ -1298,10 +1307,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="1">
-        <v>11250</v>
+        <v>9200</v>
       </c>
       <c r="C30" s="1">
-        <v>156250</v>
+        <v>111530</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>37</v>
@@ -1312,10 +1321,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="1">
-        <v>11700</v>
+        <v>9600</v>
       </c>
       <c r="C31" s="1">
-        <v>167950</v>
+        <v>121130</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>38</v>
@@ -1326,10 +1335,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="1">
-        <v>12150</v>
+        <v>10000</v>
       </c>
       <c r="C32" s="1">
-        <v>180100</v>
+        <v>131130</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>39</v>
@@ -1340,10 +1349,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="1">
-        <v>12600</v>
+        <v>10400</v>
       </c>
       <c r="C33" s="1">
-        <v>192700</v>
+        <v>141530</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>40</v>
@@ -1354,10 +1363,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="1">
-        <v>13050</v>
+        <v>10800</v>
       </c>
       <c r="C34" s="1">
-        <v>205750</v>
+        <v>152330</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>41</v>
@@ -1368,10 +1377,10 @@
         <v>31</v>
       </c>
       <c r="B35" s="1">
-        <v>13500</v>
+        <v>11200</v>
       </c>
       <c r="C35" s="1">
-        <v>219250</v>
+        <v>163530</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>42</v>
@@ -1382,10 +1391,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="1">
-        <v>13950</v>
+        <v>11600</v>
       </c>
       <c r="C36" s="1">
-        <v>233200</v>
+        <v>175130</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>43</v>
@@ -1396,10 +1405,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="1">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="C37" s="1">
-        <v>247600</v>
+        <v>187130</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>44</v>
@@ -1410,10 +1419,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="1">
-        <v>14850</v>
+        <v>12400</v>
       </c>
       <c r="C38" s="1">
-        <v>262450</v>
+        <v>199530</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>45</v>
@@ -1424,10 +1433,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="1">
-        <v>15300</v>
+        <v>12800</v>
       </c>
       <c r="C39" s="1">
-        <v>277750</v>
+        <v>212330</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>46</v>
@@ -1438,10 +1447,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="1">
-        <v>15750</v>
+        <v>13200</v>
       </c>
       <c r="C40" s="1">
-        <v>293500</v>
+        <v>225530</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>47</v>
@@ -1452,10 +1461,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="1">
-        <v>16200</v>
+        <v>13600</v>
       </c>
       <c r="C41" s="1">
-        <v>309700</v>
+        <v>239130</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>48</v>
@@ -1466,10 +1475,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="1">
-        <v>16650</v>
+        <v>14000</v>
       </c>
       <c r="C42" s="1">
-        <v>326350</v>
+        <v>253130</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>49</v>
@@ -1480,10 +1489,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="1">
-        <v>17100</v>
+        <v>14400</v>
       </c>
       <c r="C43" s="1">
-        <v>343450</v>
+        <v>267530</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>50</v>
@@ -1494,10 +1503,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="1">
-        <v>17550</v>
+        <v>14800</v>
       </c>
       <c r="C44" s="1">
-        <v>361000</v>
+        <v>282330</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>51</v>
@@ -1508,10 +1517,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="1">
-        <v>18000</v>
+        <v>15200</v>
       </c>
       <c r="C45" s="1">
-        <v>379000</v>
+        <v>297530</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>52</v>
@@ -1522,10 +1531,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="1">
-        <v>18450</v>
+        <v>15600</v>
       </c>
       <c r="C46" s="1">
-        <v>397450</v>
+        <v>313130</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>53</v>
@@ -1536,10 +1545,10 @@
         <v>43</v>
       </c>
       <c r="B47" s="1">
-        <v>18900</v>
+        <v>16000</v>
       </c>
       <c r="C47" s="1">
-        <v>416350</v>
+        <v>329130</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>54</v>
@@ -1550,10 +1559,10 @@
         <v>44</v>
       </c>
       <c r="B48" s="1">
-        <v>19350</v>
+        <v>16400</v>
       </c>
       <c r="C48" s="1">
-        <v>435700</v>
+        <v>345530</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>55</v>
@@ -1564,10 +1573,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="1">
-        <v>19800</v>
+        <v>16800</v>
       </c>
       <c r="C49" s="1">
-        <v>455500</v>
+        <v>362330</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>56</v>
@@ -1578,10 +1587,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="1">
-        <v>20250</v>
+        <v>17200</v>
       </c>
       <c r="C50" s="1">
-        <v>475750</v>
+        <v>379530</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>57</v>
@@ -1592,10 +1601,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="1">
-        <v>20700</v>
+        <v>17600</v>
       </c>
       <c r="C51" s="1">
-        <v>496450</v>
+        <v>397130</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>58</v>
@@ -1606,10 +1615,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="1">
-        <v>21150</v>
+        <v>18000</v>
       </c>
       <c r="C52" s="1">
-        <v>517600</v>
+        <v>415130</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>59</v>
@@ -1620,10 +1629,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="1">
-        <v>21600</v>
+        <v>18400</v>
       </c>
       <c r="C53" s="1">
-        <v>539200</v>
+        <v>433530</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>60</v>
@@ -1634,10 +1643,10 @@
         <v>50</v>
       </c>
       <c r="B54" s="1">
-        <v>22050</v>
+        <v>18800</v>
       </c>
       <c r="C54" s="1">
-        <v>561250</v>
+        <v>452330</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>61</v>
@@ -1648,10 +1657,10 @@
         <v>51</v>
       </c>
       <c r="B55" s="1">
-        <v>22500</v>
+        <v>19200</v>
       </c>
       <c r="C55" s="1">
-        <v>583750</v>
+        <v>471530</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>62</v>
@@ -1662,10 +1671,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="1">
-        <v>22950</v>
+        <v>19600</v>
       </c>
       <c r="C56" s="1">
-        <v>606700</v>
+        <v>491130</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>63</v>
@@ -1676,10 +1685,10 @@
         <v>53</v>
       </c>
       <c r="B57" s="1">
-        <v>23400</v>
+        <v>20000</v>
       </c>
       <c r="C57" s="1">
-        <v>630100</v>
+        <v>511130</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>64</v>
@@ -1690,10 +1699,10 @@
         <v>54</v>
       </c>
       <c r="B58" s="1">
-        <v>23850</v>
+        <v>20400</v>
       </c>
       <c r="C58" s="1">
-        <v>653950</v>
+        <v>531530</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>65</v>
@@ -1704,10 +1713,10 @@
         <v>55</v>
       </c>
       <c r="B59" s="1">
-        <v>24300</v>
+        <v>20800</v>
       </c>
       <c r="C59" s="1">
-        <v>678250</v>
+        <v>552330</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>66</v>
@@ -1718,10 +1727,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="1">
-        <v>24750</v>
+        <v>21200</v>
       </c>
       <c r="C60" s="1">
-        <v>703000</v>
+        <v>573530</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>67</v>
@@ -1732,10 +1741,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="1">
-        <v>25200</v>
+        <v>21600</v>
       </c>
       <c r="C61" s="1">
-        <v>728200</v>
+        <v>595130</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>68</v>
@@ -1746,10 +1755,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="1">
-        <v>25650</v>
+        <v>22000</v>
       </c>
       <c r="C62" s="1">
-        <v>753850</v>
+        <v>617130</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>69</v>
@@ -1760,10 +1769,10 @@
         <v>59</v>
       </c>
       <c r="B63" s="1">
-        <v>26100</v>
+        <v>22400</v>
       </c>
       <c r="C63" s="1">
-        <v>779950</v>
+        <v>639530</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>70</v>
@@ -1774,10 +1783,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="1">
-        <v>26550</v>
+        <v>22800</v>
       </c>
       <c r="C64" s="1">
-        <v>806500</v>
+        <v>662330</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>71</v>
@@ -1788,10 +1797,10 @@
         <v>61</v>
       </c>
       <c r="B65" s="1">
-        <v>27000</v>
+        <v>23200</v>
       </c>
       <c r="C65" s="1">
-        <v>833500</v>
+        <v>685530</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>72</v>
@@ -1802,10 +1811,10 @@
         <v>62</v>
       </c>
       <c r="B66" s="1">
-        <v>27450</v>
+        <v>23600</v>
       </c>
       <c r="C66" s="1">
-        <v>860950</v>
+        <v>709130</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>73</v>
@@ -1816,10 +1825,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="1">
-        <v>27900</v>
+        <v>24000</v>
       </c>
       <c r="C67" s="1">
-        <v>888850</v>
+        <v>733130</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>74</v>
@@ -1830,10 +1839,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="1">
-        <v>28350</v>
+        <v>24400</v>
       </c>
       <c r="C68" s="1">
-        <v>917200</v>
+        <v>757530</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>75</v>
@@ -1844,10 +1853,10 @@
         <v>65</v>
       </c>
       <c r="B69" s="1">
-        <v>28800</v>
+        <v>24800</v>
       </c>
       <c r="C69" s="1">
-        <v>946000</v>
+        <v>782330</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>76</v>
@@ -1858,10 +1867,10 @@
         <v>66</v>
       </c>
       <c r="B70" s="1">
-        <v>29250</v>
+        <v>25200</v>
       </c>
       <c r="C70" s="1">
-        <v>975250</v>
+        <v>807530</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>77</v>
@@ -1872,10 +1881,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="1">
-        <v>29700</v>
+        <v>25600</v>
       </c>
       <c r="C71" s="1">
-        <v>1004950</v>
+        <v>833130</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>78</v>
@@ -1886,10 +1895,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="1">
-        <v>30150</v>
+        <v>26000</v>
       </c>
       <c r="C72" s="1">
-        <v>1035100</v>
+        <v>859130</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>79</v>
@@ -1900,10 +1909,10 @@
         <v>69</v>
       </c>
       <c r="B73" s="1">
-        <v>30600</v>
+        <v>26400</v>
       </c>
       <c r="C73" s="1">
-        <v>1065700</v>
+        <v>885530</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>80</v>
@@ -1914,10 +1923,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="1">
-        <v>31050</v>
+        <v>26800</v>
       </c>
       <c r="C74" s="1">
-        <v>1096750</v>
+        <v>912330</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>81</v>
@@ -1928,10 +1937,10 @@
         <v>71</v>
       </c>
       <c r="B75" s="1">
-        <v>31500</v>
+        <v>27200</v>
       </c>
       <c r="C75" s="1">
-        <v>1128250</v>
+        <v>939530</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>82</v>
@@ -1942,10 +1951,10 @@
         <v>72</v>
       </c>
       <c r="B76" s="1">
-        <v>31950</v>
+        <v>27600</v>
       </c>
       <c r="C76" s="1">
-        <v>1160200</v>
+        <v>967130</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>83</v>
@@ -1956,10 +1965,10 @@
         <v>73</v>
       </c>
       <c r="B77" s="1">
-        <v>32400</v>
+        <v>28000</v>
       </c>
       <c r="C77" s="1">
-        <v>1192600</v>
+        <v>995130</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>84</v>
@@ -1970,10 +1979,10 @@
         <v>74</v>
       </c>
       <c r="B78" s="1">
-        <v>32850</v>
+        <v>28400</v>
       </c>
       <c r="C78" s="1">
-        <v>1225450</v>
+        <v>1023530</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>85</v>
@@ -1984,10 +1993,10 @@
         <v>75</v>
       </c>
       <c r="B79" s="1">
-        <v>33300</v>
+        <v>28800</v>
       </c>
       <c r="C79" s="1">
-        <v>1258750</v>
+        <v>1052330</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>86</v>
@@ -1998,10 +2007,10 @@
         <v>76</v>
       </c>
       <c r="B80" s="1">
-        <v>33750</v>
+        <v>29200</v>
       </c>
       <c r="C80" s="1">
-        <v>1292500</v>
+        <v>1081530</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>87</v>
@@ -2012,10 +2021,10 @@
         <v>77</v>
       </c>
       <c r="B81" s="1">
-        <v>34200</v>
+        <v>29600</v>
       </c>
       <c r="C81" s="1">
-        <v>1326700</v>
+        <v>1111130</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>88</v>
@@ -2026,10 +2035,10 @@
         <v>78</v>
       </c>
       <c r="B82" s="1">
-        <v>34650</v>
+        <v>30000</v>
       </c>
       <c r="C82" s="1">
-        <v>1361350</v>
+        <v>1141130</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>89</v>
@@ -2040,10 +2049,10 @@
         <v>79</v>
       </c>
       <c r="B83" s="1">
-        <v>35100</v>
+        <v>30400</v>
       </c>
       <c r="C83" s="1">
-        <v>1396450</v>
+        <v>1171530</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>90</v>
@@ -2054,10 +2063,10 @@
         <v>80</v>
       </c>
       <c r="B84" s="1">
-        <v>35550</v>
+        <v>30800</v>
       </c>
       <c r="C84" s="1">
-        <v>1432000</v>
+        <v>1202330</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>91</v>
@@ -2068,10 +2077,10 @@
         <v>81</v>
       </c>
       <c r="B85" s="1">
-        <v>36000</v>
+        <v>31200</v>
       </c>
       <c r="C85" s="1">
-        <v>1468000</v>
+        <v>1233530</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>92</v>
@@ -2082,10 +2091,10 @@
         <v>82</v>
       </c>
       <c r="B86" s="1">
-        <v>36450</v>
+        <v>31600</v>
       </c>
       <c r="C86" s="1">
-        <v>1504450</v>
+        <v>1265130</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>93</v>
@@ -2096,10 +2105,10 @@
         <v>83</v>
       </c>
       <c r="B87" s="1">
-        <v>36900</v>
+        <v>32000</v>
       </c>
       <c r="C87" s="1">
-        <v>1541350</v>
+        <v>1297130</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>94</v>
@@ -2110,10 +2119,10 @@
         <v>84</v>
       </c>
       <c r="B88" s="1">
-        <v>37350</v>
+        <v>32400</v>
       </c>
       <c r="C88" s="1">
-        <v>1578700</v>
+        <v>1329530</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>95</v>
@@ -2124,10 +2133,10 @@
         <v>85</v>
       </c>
       <c r="B89" s="1">
-        <v>37800</v>
+        <v>32800</v>
       </c>
       <c r="C89" s="1">
-        <v>1616500</v>
+        <v>1362330</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>96</v>
@@ -2138,10 +2147,10 @@
         <v>86</v>
       </c>
       <c r="B90" s="1">
-        <v>38250</v>
+        <v>33200</v>
       </c>
       <c r="C90" s="1">
-        <v>1654750</v>
+        <v>1395530</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>97</v>
@@ -2152,10 +2161,10 @@
         <v>87</v>
       </c>
       <c r="B91" s="1">
-        <v>38700</v>
+        <v>33600</v>
       </c>
       <c r="C91" s="1">
-        <v>1693450</v>
+        <v>1429130</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>98</v>
@@ -2166,10 +2175,10 @@
         <v>88</v>
       </c>
       <c r="B92" s="1">
-        <v>39150</v>
+        <v>34000</v>
       </c>
       <c r="C92" s="1">
-        <v>1732600</v>
+        <v>1463130</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>99</v>
@@ -2180,10 +2189,10 @@
         <v>89</v>
       </c>
       <c r="B93" s="1">
-        <v>39600</v>
+        <v>34400</v>
       </c>
       <c r="C93" s="1">
-        <v>1772200</v>
+        <v>1497530</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>100</v>
@@ -2194,10 +2203,10 @@
         <v>90</v>
       </c>
       <c r="B94" s="1">
-        <v>40050</v>
+        <v>34800</v>
       </c>
       <c r="C94" s="1">
-        <v>1812250</v>
+        <v>1532330</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>101</v>
@@ -2208,10 +2217,10 @@
         <v>91</v>
       </c>
       <c r="B95" s="1">
-        <v>40500</v>
+        <v>35200</v>
       </c>
       <c r="C95" s="1">
-        <v>1852750</v>
+        <v>1567530</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>102</v>
@@ -2222,10 +2231,10 @@
         <v>92</v>
       </c>
       <c r="B96" s="1">
-        <v>40950</v>
+        <v>35600</v>
       </c>
       <c r="C96" s="1">
-        <v>1893700</v>
+        <v>1603130</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>103</v>
@@ -2236,10 +2245,10 @@
         <v>93</v>
       </c>
       <c r="B97" s="1">
-        <v>41400</v>
+        <v>36000</v>
       </c>
       <c r="C97" s="1">
-        <v>1935100</v>
+        <v>1639130</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>104</v>
@@ -2250,10 +2259,10 @@
         <v>94</v>
       </c>
       <c r="B98" s="1">
-        <v>41850</v>
+        <v>36400</v>
       </c>
       <c r="C98" s="1">
-        <v>1976950</v>
+        <v>1675530</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>105</v>
@@ -2264,10 +2273,10 @@
         <v>95</v>
       </c>
       <c r="B99" s="1">
-        <v>42300</v>
+        <v>36800</v>
       </c>
       <c r="C99" s="1">
-        <v>2019250</v>
+        <v>1712330</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>106</v>
@@ -2278,10 +2287,10 @@
         <v>96</v>
       </c>
       <c r="B100" s="1">
-        <v>42750</v>
+        <v>37200</v>
       </c>
       <c r="C100" s="1">
-        <v>2062000</v>
+        <v>1749530</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>107</v>
@@ -2292,10 +2301,10 @@
         <v>97</v>
       </c>
       <c r="B101" s="1">
-        <v>43200</v>
+        <v>37600</v>
       </c>
       <c r="C101" s="1">
-        <v>2105200</v>
+        <v>1787130</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>108</v>
@@ -2306,10 +2315,10 @@
         <v>98</v>
       </c>
       <c r="B102" s="1">
-        <v>43650</v>
+        <v>38000</v>
       </c>
       <c r="C102" s="1">
-        <v>2148850</v>
+        <v>1825130</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>109</v>
@@ -2320,10 +2329,10 @@
         <v>99</v>
       </c>
       <c r="B103" s="1">
-        <v>44100</v>
+        <v>38400</v>
       </c>
       <c r="C103" s="1">
-        <v>2192950</v>
+        <v>1863530</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>110</v>
@@ -2334,10 +2343,10 @@
         <v>100</v>
       </c>
       <c r="B104" s="1">
-        <v>44550</v>
+        <v>38800</v>
       </c>
       <c r="C104" s="1">
-        <v>2237500</v>
+        <v>1902330</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>111</v>
@@ -2348,10 +2357,10 @@
         <v>101</v>
       </c>
       <c r="B105" s="1">
-        <v>45000</v>
+        <v>39200</v>
       </c>
       <c r="C105" s="1">
-        <v>2282500</v>
+        <v>1941530</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>112</v>
@@ -2362,10 +2371,10 @@
         <v>102</v>
       </c>
       <c r="B106" s="1">
-        <v>45450</v>
+        <v>39600</v>
       </c>
       <c r="C106" s="1">
-        <v>2327950</v>
+        <v>1981130</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>113</v>
@@ -2376,10 +2385,10 @@
         <v>103</v>
       </c>
       <c r="B107" s="1">
-        <v>45900</v>
+        <v>40000</v>
       </c>
       <c r="C107" s="1">
-        <v>2373850</v>
+        <v>2021130</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>114</v>
@@ -2390,10 +2399,10 @@
         <v>104</v>
       </c>
       <c r="B108" s="1">
-        <v>46350</v>
+        <v>40400</v>
       </c>
       <c r="C108" s="1">
-        <v>2420200</v>
+        <v>2061530</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>115</v>
@@ -2404,10 +2413,10 @@
         <v>105</v>
       </c>
       <c r="B109" s="1">
-        <v>46800</v>
+        <v>40800</v>
       </c>
       <c r="C109" s="1">
-        <v>2467000</v>
+        <v>2102330</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>116</v>
@@ -2418,10 +2427,10 @@
         <v>106</v>
       </c>
       <c r="B110" s="1">
-        <v>47250</v>
+        <v>41200</v>
       </c>
       <c r="C110" s="1">
-        <v>2514250</v>
+        <v>2143530</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>117</v>
@@ -2432,10 +2441,10 @@
         <v>107</v>
       </c>
       <c r="B111" s="1">
-        <v>47700</v>
+        <v>41600</v>
       </c>
       <c r="C111" s="1">
-        <v>2561950</v>
+        <v>2185130</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>118</v>
@@ -2446,10 +2455,10 @@
         <v>108</v>
       </c>
       <c r="B112" s="1">
-        <v>48150</v>
+        <v>42000</v>
       </c>
       <c r="C112" s="1">
-        <v>2610100</v>
+        <v>2227130</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>119</v>
@@ -2460,10 +2469,10 @@
         <v>109</v>
       </c>
       <c r="B113" s="1">
-        <v>48600</v>
+        <v>42400</v>
       </c>
       <c r="C113" s="1">
-        <v>2658700</v>
+        <v>2269530</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>120</v>
@@ -2474,10 +2483,10 @@
         <v>110</v>
       </c>
       <c r="B114" s="1">
-        <v>49050</v>
+        <v>42800</v>
       </c>
       <c r="C114" s="1">
-        <v>2707750</v>
+        <v>2312330</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>121</v>
@@ -2488,10 +2497,10 @@
         <v>111</v>
       </c>
       <c r="B115" s="1">
-        <v>49500</v>
+        <v>43200</v>
       </c>
       <c r="C115" s="1">
-        <v>2757250</v>
+        <v>2355530</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>122</v>
@@ -2502,10 +2511,10 @@
         <v>112</v>
       </c>
       <c r="B116" s="1">
-        <v>49950</v>
+        <v>43600</v>
       </c>
       <c r="C116" s="1">
-        <v>2807200</v>
+        <v>2399130</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>123</v>
@@ -2516,10 +2525,10 @@
         <v>113</v>
       </c>
       <c r="B117" s="1">
-        <v>50400</v>
+        <v>44000</v>
       </c>
       <c r="C117" s="1">
-        <v>2857600</v>
+        <v>2443130</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>124</v>
@@ -2530,10 +2539,10 @@
         <v>114</v>
       </c>
       <c r="B118" s="1">
-        <v>50850</v>
+        <v>44400</v>
       </c>
       <c r="C118" s="1">
-        <v>2908450</v>
+        <v>2487530</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>125</v>
@@ -2544,10 +2553,10 @@
         <v>115</v>
       </c>
       <c r="B119" s="1">
-        <v>51300</v>
+        <v>44800</v>
       </c>
       <c r="C119" s="1">
-        <v>2959750</v>
+        <v>2532330</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>126</v>
@@ -2558,10 +2567,10 @@
         <v>116</v>
       </c>
       <c r="B120" s="1">
-        <v>51750</v>
+        <v>45200</v>
       </c>
       <c r="C120" s="1">
-        <v>3011500</v>
+        <v>2577530</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>127</v>
@@ -2572,10 +2581,10 @@
         <v>117</v>
       </c>
       <c r="B121" s="1">
-        <v>52200</v>
+        <v>45600</v>
       </c>
       <c r="C121" s="1">
-        <v>3063700</v>
+        <v>2623130</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>128</v>
@@ -2586,10 +2595,10 @@
         <v>118</v>
       </c>
       <c r="B122" s="1">
-        <v>52650</v>
+        <v>46000</v>
       </c>
       <c r="C122" s="1">
-        <v>3116350</v>
+        <v>2669130</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>129</v>
@@ -2600,10 +2609,10 @@
         <v>119</v>
       </c>
       <c r="B123" s="1">
-        <v>53100</v>
+        <v>46400</v>
       </c>
       <c r="C123" s="1">
-        <v>3169450</v>
+        <v>2715530</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>130</v>
@@ -2614,10 +2623,10 @@
         <v>120</v>
       </c>
       <c r="B124" s="1">
-        <v>53550</v>
+        <v>46800</v>
       </c>
       <c r="C124" s="1">
-        <v>3223000</v>
+        <v>2762330</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>131</v>
@@ -2628,10 +2637,10 @@
         <v>121</v>
       </c>
       <c r="B125" s="1">
-        <v>54000</v>
+        <v>47200</v>
       </c>
       <c r="C125" s="1">
-        <v>3277000</v>
+        <v>2809530</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>132</v>
@@ -2642,10 +2651,10 @@
         <v>122</v>
       </c>
       <c r="B126" s="1">
-        <v>54450</v>
+        <v>47600</v>
       </c>
       <c r="C126" s="1">
-        <v>3331450</v>
+        <v>2857130</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>133</v>
@@ -2656,10 +2665,10 @@
         <v>123</v>
       </c>
       <c r="B127" s="1">
-        <v>54900</v>
+        <v>48000</v>
       </c>
       <c r="C127" s="1">
-        <v>3386350</v>
+        <v>2905130</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>134</v>
@@ -2670,10 +2679,10 @@
         <v>124</v>
       </c>
       <c r="B128" s="1">
-        <v>55350</v>
+        <v>48400</v>
       </c>
       <c r="C128" s="1">
-        <v>3441700</v>
+        <v>2953530</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>135</v>
@@ -2684,10 +2693,10 @@
         <v>125</v>
       </c>
       <c r="B129" s="1">
-        <v>55800</v>
+        <v>48800</v>
       </c>
       <c r="C129" s="1">
-        <v>3497500</v>
+        <v>3002330</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>136</v>
@@ -2698,10 +2707,10 @@
         <v>126</v>
       </c>
       <c r="B130" s="1">
-        <v>56250</v>
+        <v>49200</v>
       </c>
       <c r="C130" s="1">
-        <v>3553750</v>
+        <v>3051530</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>137</v>
@@ -2712,10 +2721,10 @@
         <v>127</v>
       </c>
       <c r="B131" s="1">
-        <v>56700</v>
+        <v>49600</v>
       </c>
       <c r="C131" s="1">
-        <v>3610450</v>
+        <v>3101130</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>138</v>
@@ -2726,10 +2735,10 @@
         <v>128</v>
       </c>
       <c r="B132" s="1">
-        <v>57150</v>
+        <v>50000</v>
       </c>
       <c r="C132" s="1">
-        <v>3667600</v>
+        <v>3151130</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>139</v>
@@ -2740,10 +2749,10 @@
         <v>129</v>
       </c>
       <c r="B133" s="1">
-        <v>57600</v>
+        <v>50400</v>
       </c>
       <c r="C133" s="1">
-        <v>3725200</v>
+        <v>3201530</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>140</v>
@@ -2754,10 +2763,10 @@
         <v>130</v>
       </c>
       <c r="B134" s="1">
-        <v>58050</v>
+        <v>50800</v>
       </c>
       <c r="C134" s="1">
-        <v>3783250</v>
+        <v>3252330</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>141</v>
@@ -2768,10 +2777,10 @@
         <v>131</v>
       </c>
       <c r="B135" s="1">
-        <v>58500</v>
+        <v>51200</v>
       </c>
       <c r="C135" s="1">
-        <v>3841750</v>
+        <v>3303530</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>142</v>
@@ -2782,10 +2791,10 @@
         <v>132</v>
       </c>
       <c r="B136" s="1">
-        <v>58950</v>
+        <v>51600</v>
       </c>
       <c r="C136" s="1">
-        <v>3900700</v>
+        <v>3355130</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>143</v>
@@ -2796,10 +2805,10 @@
         <v>133</v>
       </c>
       <c r="B137" s="1">
-        <v>59400</v>
+        <v>52000</v>
       </c>
       <c r="C137" s="1">
-        <v>3960100</v>
+        <v>3407130</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>144</v>
@@ -2810,10 +2819,10 @@
         <v>134</v>
       </c>
       <c r="B138" s="1">
-        <v>59850</v>
+        <v>52400</v>
       </c>
       <c r="C138" s="1">
-        <v>4019950</v>
+        <v>3459530</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>145</v>
@@ -2824,10 +2833,10 @@
         <v>135</v>
       </c>
       <c r="B139" s="1">
-        <v>60300</v>
+        <v>52800</v>
       </c>
       <c r="C139" s="1">
-        <v>4080250</v>
+        <v>3512330</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>146</v>
@@ -2838,10 +2847,10 @@
         <v>136</v>
       </c>
       <c r="B140" s="1">
-        <v>60750</v>
+        <v>53200</v>
       </c>
       <c r="C140" s="1">
-        <v>4141000</v>
+        <v>3565530</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>147</v>
@@ -2852,10 +2861,10 @@
         <v>137</v>
       </c>
       <c r="B141" s="1">
-        <v>61200</v>
+        <v>53600</v>
       </c>
       <c r="C141" s="1">
-        <v>4202200</v>
+        <v>3619130</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>148</v>
@@ -2866,10 +2875,10 @@
         <v>138</v>
       </c>
       <c r="B142" s="1">
-        <v>61650</v>
+        <v>54000</v>
       </c>
       <c r="C142" s="1">
-        <v>4263850</v>
+        <v>3673130</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>149</v>
@@ -2880,10 +2889,10 @@
         <v>139</v>
       </c>
       <c r="B143" s="1">
-        <v>62100</v>
+        <v>54400</v>
       </c>
       <c r="C143" s="1">
-        <v>4325950</v>
+        <v>3727530</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>150</v>
@@ -2894,10 +2903,10 @@
         <v>140</v>
       </c>
       <c r="B144" s="1">
-        <v>62550</v>
+        <v>54800</v>
       </c>
       <c r="C144" s="1">
-        <v>4388500</v>
+        <v>3782330</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>151</v>
@@ -2908,10 +2917,10 @@
         <v>141</v>
       </c>
       <c r="B145" s="1">
-        <v>63000</v>
+        <v>55200</v>
       </c>
       <c r="C145" s="1">
-        <v>4451500</v>
+        <v>3837530</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>152</v>
@@ -2922,10 +2931,10 @@
         <v>142</v>
       </c>
       <c r="B146" s="1">
-        <v>63450</v>
+        <v>55600</v>
       </c>
       <c r="C146" s="1">
-        <v>4514950</v>
+        <v>3893130</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>153</v>
@@ -2936,10 +2945,10 @@
         <v>143</v>
       </c>
       <c r="B147" s="1">
-        <v>63900</v>
+        <v>56000</v>
       </c>
       <c r="C147" s="1">
-        <v>4578850</v>
+        <v>3949130</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>154</v>
@@ -2950,10 +2959,10 @@
         <v>144</v>
       </c>
       <c r="B148" s="1">
-        <v>64350</v>
+        <v>56400</v>
       </c>
       <c r="C148" s="1">
-        <v>4643200</v>
+        <v>4005530</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>155</v>
@@ -2964,10 +2973,10 @@
         <v>145</v>
       </c>
       <c r="B149" s="1">
-        <v>64800</v>
+        <v>56800</v>
       </c>
       <c r="C149" s="1">
-        <v>4708000</v>
+        <v>4062330</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>156</v>
@@ -2978,10 +2987,10 @@
         <v>146</v>
       </c>
       <c r="B150" s="1">
-        <v>65250</v>
+        <v>57200</v>
       </c>
       <c r="C150" s="1">
-        <v>4773250</v>
+        <v>4119530</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>157</v>
@@ -2992,10 +3001,10 @@
         <v>147</v>
       </c>
       <c r="B151" s="1">
-        <v>65700</v>
+        <v>57600</v>
       </c>
       <c r="C151" s="1">
-        <v>4838950</v>
+        <v>4177130</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>158</v>
@@ -3006,10 +3015,10 @@
         <v>148</v>
       </c>
       <c r="B152" s="1">
-        <v>66150</v>
+        <v>58000</v>
       </c>
       <c r="C152" s="1">
-        <v>4905100</v>
+        <v>4235130</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>159</v>
@@ -3020,10 +3029,10 @@
         <v>149</v>
       </c>
       <c r="B153" s="1">
-        <v>66600</v>
+        <v>58400</v>
       </c>
       <c r="C153" s="1">
-        <v>4971700</v>
+        <v>4293530</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>160</v>
@@ -3034,10 +3043,10 @@
         <v>150</v>
       </c>
       <c r="B154" s="1">
-        <v>67050</v>
+        <v>58800</v>
       </c>
       <c r="C154" s="1">
-        <v>5038750</v>
+        <v>4352330</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>161</v>
@@ -3048,10 +3057,10 @@
         <v>151</v>
       </c>
       <c r="B155" s="1">
-        <v>67500</v>
+        <v>59200</v>
       </c>
       <c r="C155" s="1">
-        <v>5106250</v>
+        <v>4411530</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>162</v>
@@ -3062,10 +3071,10 @@
         <v>152</v>
       </c>
       <c r="B156" s="1">
-        <v>67950</v>
+        <v>59600</v>
       </c>
       <c r="C156" s="1">
-        <v>5174200</v>
+        <v>4471130</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>163</v>
@@ -3076,10 +3085,10 @@
         <v>153</v>
       </c>
       <c r="B157" s="1">
-        <v>68400</v>
+        <v>60000</v>
       </c>
       <c r="C157" s="1">
-        <v>5242600</v>
+        <v>4531130</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>164</v>
@@ -3090,10 +3099,10 @@
         <v>154</v>
       </c>
       <c r="B158" s="1">
-        <v>68850</v>
+        <v>60400</v>
       </c>
       <c r="C158" s="1">
-        <v>5311450</v>
+        <v>4591530</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>165</v>
@@ -3104,10 +3113,10 @@
         <v>155</v>
       </c>
       <c r="B159" s="1">
-        <v>69300</v>
+        <v>60800</v>
       </c>
       <c r="C159" s="1">
-        <v>5380750</v>
+        <v>4652330</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>166</v>
@@ -3118,10 +3127,10 @@
         <v>156</v>
       </c>
       <c r="B160" s="1">
-        <v>69750</v>
+        <v>61200</v>
       </c>
       <c r="C160" s="1">
-        <v>5450500</v>
+        <v>4713530</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>167</v>
@@ -3132,10 +3141,10 @@
         <v>157</v>
       </c>
       <c r="B161" s="1">
-        <v>70200</v>
+        <v>61600</v>
       </c>
       <c r="C161" s="1">
-        <v>5520700</v>
+        <v>4775130</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>168</v>
@@ -3146,10 +3155,10 @@
         <v>158</v>
       </c>
       <c r="B162" s="1">
-        <v>70650</v>
+        <v>62000</v>
       </c>
       <c r="C162" s="1">
-        <v>5591350</v>
+        <v>4837130</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>169</v>
@@ -3160,10 +3169,10 @@
         <v>159</v>
       </c>
       <c r="B163" s="1">
-        <v>71100</v>
+        <v>62400</v>
       </c>
       <c r="C163" s="1">
-        <v>5662450</v>
+        <v>4899530</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>170</v>
@@ -3177,7 +3186,7 @@
         <v>-1</v>
       </c>
       <c r="C164" s="1">
-        <v>5662450</v>
+        <v>4899530</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>171</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3F826A-32A0-44C1-9943-6C85BFBDAB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B07DB6-6B15-469A-85EE-0C9938A8847F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_level_v8" sheetId="1" r:id="rId1"/>
@@ -82,484 +82,484 @@
     <t>MAP&lt;INT:LONG&gt;_C_S</t>
   </si>
   <si>
-    <t>3010101:1_3020101:1_3030101:20_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:2_3020101:2_3030101:40_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:3_3020101:3_3030101:60_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:4_3020101:4_3030101:80_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:5_3020101:5_3030101:104_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:7_3020101:7_3030101:137_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:9_3020101:9_3030101:180_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:12_3020101:12_3030101:235_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:15_3020101:15_3030101:302_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:20_3020101:20_3030101:401_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:29_3020101:29_3030101:581_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:43_3020101:43_3030101:866_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:64_3020101:64_3030101:1283_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:93_3020101:93_3030101:1859_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:131_3020101:131_3030101:2620_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:180_3020101:180_3030101:3593_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:241_3020101:241_3030101:4805_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:315_3020101:315_3030101:6282_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:403_3020101:403_3030101:8051_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:507_3020101:507_3030101:10139_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:629_3020101:629_3030101:12572_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:769_3020101:769_3030101:15377_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:929_3020101:929_3030101:18581_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:1110_3020101:1110_3030101:22210_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:1314_3020101:1314_3030101:26291_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:1542_3020101:1542_3030101:30851_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:1795_3020101:1795_3030101:35916_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:2075_3020101:2075_3030101:41513_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:2383_3020101:2383_3030101:47669_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:2720_3020101:2720_3030101:54410_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:3088_3020101:3088_3030101:61763_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:3488_3020101:3488_3030101:69755_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:3921_3020101:3921_3030101:78412_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:4388_3020101:4388_3030101:87761_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:4891_3020101:4891_3030101:97829_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:5432_3020101:5432_3030101:108642_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:6011_3020101:6011_3030101:120227_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:6630_3020101:6630_3030101:132611_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:7290_3020101:7290_3030101:145820_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:7993_3020101:7993_3030101:159881_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:8740_3020101:8740_3030101:174821_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:9532_3020101:9532_3030101:190666_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:10371_3020101:10371_3030101:207443_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:11258_3020101:11258_3030101:225179_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:12194_3020101:12194_3030101:243900_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:13181_3020101:13181_3030101:263633_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:14220_3020101:14220_3030101:284406_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:15313_3020101:15313_3030101:306273_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:16463_3020101:16463_3030101:329273_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:17672_3020101:17672_3030101:353446_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:18942_3020101:18942_3030101:378846_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:20275_3020101:20275_3030101:405513_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:21674_3020101:21674_3030101:433500_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:23142_3020101:23142_3030101:462860_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:24681_3020101:24681_3030101:493647_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:26294_3020101:26294_3030101:525914_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:27984_3020101:27984_3030101:559714_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:29753_3020101:29753_3030101:595101_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:31605_3020101:31605_3030101:632141_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:33542_3020101:33542_3030101:670888_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:35568_3020101:35568_3030101:711408_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:37686_3020101:37686_3030101:753768_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:39899_3020101:39899_3030101:798021_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:42210_3020101:42210_3030101:844234_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:44623_3020101:44623_3030101:892487_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:47141_3020101:47141_3030101:942847_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:49768_3020101:49768_3030101:995380_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:52507_3020101:52507_3030101:1050167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:55363_3020101:55363_3030101:1107287_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:58340_3020101:58340_3030101:1166820_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:61441_3020101:61441_3030101:1228847_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:64671_3020101:64671_3030101:1293447_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:68034_3020101:68034_3030101:1360700_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:71534_3020101:71534_3030101:1430700_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:75176_3020101:75176_3030101:1503540_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:78965_3020101:78965_3030101:1579313_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:82905_3020101:82905_3030101:1658113_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:87001_3020101:87001_3030101:1740033_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:91258_3020101:91258_3030101:1825180_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:95682_3020101:95682_3030101:1913660_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:100278_3020101:100278_3030101:2005580_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:105051_3020101:105051_3030101:2101047_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:110007_3020101:110007_3030101:2200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:115007_3020101:115007_3030101:2300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:120007_3020101:120007_3030101:2400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:125007_3020101:125007_3030101:2500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:130007_3020101:130007_3030101:2600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:135007_3020101:135007_3030101:2700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:140007_3020101:140007_3030101:2800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:145007_3020101:145007_3030101:2900167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:150007_3020101:150007_3030101:3000167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:155007_3020101:155007_3030101:3100167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:160007_3020101:160007_3030101:3200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:165007_3020101:165007_3030101:3300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:170007_3020101:170007_3030101:3400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:175007_3020101:175007_3030101:3500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:180007_3020101:180007_3030101:3600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:185007_3020101:185007_3030101:3700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:190007_3020101:190007_3030101:3800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:195007_3020101:195007_3030101:3900167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:200007_3020101:200007_3030101:4000167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:205007_3020101:205007_3030101:4100167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:210007_3020101:210007_3030101:4200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:215007_3020101:215007_3030101:4300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:220007_3020101:220007_3030101:4400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:225007_3020101:225007_3030101:4500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:230007_3020101:230007_3030101:4600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:235007_3020101:235007_3030101:4700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:240007_3020101:240007_3030101:4800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:245007_3020101:245007_3030101:4900167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:250007_3020101:250007_3030101:5000167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:255007_3020101:255007_3030101:5100167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:260007_3020101:260007_3030101:5200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:265007_3020101:265007_3030101:5300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:270007_3020101:270007_3030101:5400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:275007_3020101:275007_3030101:5500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:280007_3020101:280007_3030101:5600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:285007_3020101:285007_3030101:5700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:290007_3020101:290007_3030101:5800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:295007_3020101:295007_3030101:5900167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:300007_3020101:300007_3030101:6000167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:305007_3020101:305007_3030101:6100167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:310007_3020101:310007_3030101:6200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:315007_3020101:315007_3030101:6300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:320007_3020101:320007_3030101:6400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:325007_3020101:325007_3030101:6500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:330007_3020101:330007_3030101:6600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:335007_3020101:335007_3030101:6700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:340007_3020101:340007_3030101:6800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:345007_3020101:345007_3030101:6900167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:350007_3020101:350007_3030101:7000167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:355007_3020101:355007_3030101:7100167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:360007_3020101:360007_3030101:7200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:365007_3020101:365007_3030101:7300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:370007_3020101:370007_3030101:7400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:375007_3020101:375007_3030101:7500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:380007_3020101:380007_3030101:7600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:385007_3020101:385007_3030101:7700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:390007_3020101:390007_3030101:7800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:395007_3020101:395007_3030101:7900167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:400007_3020101:400007_3030101:8000167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:405007_3020101:405007_3030101:8100167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:410007_3020101:410007_3030101:8200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:415007_3020101:415007_3030101:8300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:420007_3020101:420007_3030101:8400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:425007_3020101:425007_3030101:8500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:430007_3020101:430007_3030101:8600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:435007_3020101:435007_3030101:8700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:440007_3020101:440007_3030101:8800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:445007_3020101:445007_3030101:8900167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:450007_3020101:450007_3030101:9000167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:455007_3020101:455007_3030101:9100167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:460007_3020101:460007_3030101:9200167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:465007_3020101:465007_3030101:9300167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:470007_3020101:470007_3030101:9400167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:475007_3020101:475007_3030101:9500167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:480007_3020101:480007_3030101:9600167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:485007_3020101:485007_3030101:9700167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:490007_3020101:490007_3030101:9800167_9101:3</t>
-  </si>
-  <si>
-    <t>3010101:495007_3020101:495007_3030101:9900167_9101:3</t>
+    <t>3010101:5_3020101:1_3030101:80_9101:20</t>
+  </si>
+  <si>
+    <t>3010101:14_3020101:3_3030101:224_9101:56</t>
+  </si>
+  <si>
+    <t>3010101:29_3020101:6_3030101:464_9101:116</t>
+  </si>
+  <si>
+    <t>3010101:52_3020101:10_3030101:824_9101:206</t>
+  </si>
+  <si>
+    <t>3010101:83_3020101:17_3030101:1328_9101:332</t>
+  </si>
+  <si>
+    <t>3010101:125_3020101:25_3030101:1992_9101:498</t>
+  </si>
+  <si>
+    <t>3010101:176_3020101:35_3030101:2816_9101:704</t>
+  </si>
+  <si>
+    <t>3010101:238_3020101:48_3030101:3800_9101:950</t>
+  </si>
+  <si>
+    <t>3010101:309_3020101:62_3030101:4944_9101:1236</t>
+  </si>
+  <si>
+    <t>3010101:391_3020101:78_3030101:6248_9101:1562</t>
+  </si>
+  <si>
+    <t>3010101:497_3020101:99_3030101:7952_9101:1988</t>
+  </si>
+  <si>
+    <t>3010101:615_3020101:123_3030101:9832_9101:2458</t>
+  </si>
+  <si>
+    <t>3010101:743_3020101:149_3030101:11888_9101:2972</t>
+  </si>
+  <si>
+    <t>3010101:883_3020101:177_3030101:14120_9101:3530</t>
+  </si>
+  <si>
+    <t>3010101:1033_3020101:207_3030101:16528_9101:4132</t>
+  </si>
+  <si>
+    <t>3010101:1195_3020101:239_3030101:19112_9101:4778</t>
+  </si>
+  <si>
+    <t>3010101:1367_3020101:273_3030101:21872_9101:5468</t>
+  </si>
+  <si>
+    <t>3010101:1551_3020101:310_3030101:24808_9101:6202</t>
+  </si>
+  <si>
+    <t>3010101:1745_3020101:349_3030101:27920_9101:6980</t>
+  </si>
+  <si>
+    <t>3010101:1951_3020101:390_3030101:31208_9101:7802</t>
+  </si>
+  <si>
+    <t>3010101:2184_3020101:437_3030101:34936_9101:8734</t>
+  </si>
+  <si>
+    <t>3010101:2429_3020101:486_3030101:38856_9101:9714</t>
+  </si>
+  <si>
+    <t>3010101:2686_3020101:537_3030101:42968_9101:10742</t>
+  </si>
+  <si>
+    <t>3010101:2955_3020101:591_3030101:47272_9101:11818</t>
+  </si>
+  <si>
+    <t>3010101:3236_3020101:647_3030101:51768_9101:12942</t>
+  </si>
+  <si>
+    <t>3010101:3529_3020101:706_3030101:56456_9101:14114</t>
+  </si>
+  <si>
+    <t>3010101:3834_3020101:767_3030101:61336_9101:15334</t>
+  </si>
+  <si>
+    <t>3010101:4151_3020101:830_3030101:66408_9101:16602</t>
+  </si>
+  <si>
+    <t>3010101:4480_3020101:896_3030101:71680_9101:17920</t>
+  </si>
+  <si>
+    <t>3010101:4823_3020101:965_3030101:77160_9101:19290</t>
+  </si>
+  <si>
+    <t>3010101:5200_3020101:1040_3030101:83192_9101:20798</t>
+  </si>
+  <si>
+    <t>3010101:5592_3020101:1118_3030101:89464_9101:22366</t>
+  </si>
+  <si>
+    <t>3010101:5999_3020101:1200_3030101:95984_9101:23996</t>
+  </si>
+  <si>
+    <t>3010101:6423_3020101:1285_3030101:102768_9101:25692</t>
+  </si>
+  <si>
+    <t>3010101:6864_3020101:1373_3030101:109824_9101:27456</t>
+  </si>
+  <si>
+    <t>3010101:7323_3020101:1465_3030101:117160_9101:29290</t>
+  </si>
+  <si>
+    <t>3010101:7800_3020101:1560_3030101:124792_9101:31198</t>
+  </si>
+  <si>
+    <t>3010101:8296_3020101:1659_3030101:132728_9101:33182</t>
+  </si>
+  <si>
+    <t>3010101:8812_3020101:1762_3030101:140984_9101:35246</t>
+  </si>
+  <si>
+    <t>3010101:9348_3020101:1870_3030101:149568_9101:37392</t>
+  </si>
+  <si>
+    <t>3010101:9938_3020101:1988_3030101:159008_9101:39752</t>
+  </si>
+  <si>
+    <t>3010101:10552_3020101:2110_3030101:168824_9101:42206</t>
+  </si>
+  <si>
+    <t>3010101:11190_3020101:2238_3030101:179032_9101:44758</t>
+  </si>
+  <si>
+    <t>3010101:11853_3020101:2371_3030101:189648_9101:47412</t>
+  </si>
+  <si>
+    <t>3010101:12543_3020101:2509_3030101:200688_9101:50172</t>
+  </si>
+  <si>
+    <t>3010101:13261_3020101:2652_3030101:212168_9101:53042</t>
+  </si>
+  <si>
+    <t>3010101:14007_3020101:2801_3030101:224104_9101:56026</t>
+  </si>
+  <si>
+    <t>3010101:14783_3020101:2957_3030101:236520_9101:59130</t>
+  </si>
+  <si>
+    <t>3010101:15590_3020101:3118_3030101:249432_9101:62358</t>
+  </si>
+  <si>
+    <t>3010101:16429_3020101:3286_3030101:262864_9101:65716</t>
+  </si>
+  <si>
+    <t>3010101:17353_3020101:3471_3030101:277640_9101:69410</t>
+  </si>
+  <si>
+    <t>3010101:18313_3020101:3663_3030101:293008_9101:73252</t>
+  </si>
+  <si>
+    <t>3010101:19312_3020101:3862_3030101:308992_9101:77248</t>
+  </si>
+  <si>
+    <t>3010101:20351_3020101:4070_3030101:325616_9101:81404</t>
+  </si>
+  <si>
+    <t>3010101:21432_3020101:4286_3030101:342904_9101:85726</t>
+  </si>
+  <si>
+    <t>3010101:22555_3020101:4511_3030101:360880_9101:90220</t>
+  </si>
+  <si>
+    <t>3010101:23724_3020101:4745_3030101:379576_9101:94894</t>
+  </si>
+  <si>
+    <t>3010101:24939_3020101:4988_3030101:399016_9101:99754</t>
+  </si>
+  <si>
+    <t>3010101:26202_3020101:5240_3030101:419232_9101:104808</t>
+  </si>
+  <si>
+    <t>3010101:27516_3020101:5503_3030101:440256_9101:110064</t>
+  </si>
+  <si>
+    <t>3010101:28962_3020101:5792_3030101:463384_9101:115846</t>
+  </si>
+  <si>
+    <t>3010101:30465_3020101:6093_3030101:487440_9101:121860</t>
+  </si>
+  <si>
+    <t>3010101:32029_3020101:6406_3030101:512456_9101:128114</t>
+  </si>
+  <si>
+    <t>3010101:33655_3020101:6731_3030101:538472_9101:134618</t>
+  </si>
+  <si>
+    <t>3010101:35346_3020101:7069_3030101:565528_9101:141382</t>
+  </si>
+  <si>
+    <t>3010101:37104_3020101:7421_3030101:593664_9101:148416</t>
+  </si>
+  <si>
+    <t>3010101:38933_3020101:7787_3030101:622928_9101:155732</t>
+  </si>
+  <si>
+    <t>3010101:40835_3020101:8167_3030101:653360_9101:163340</t>
+  </si>
+  <si>
+    <t>3010101:42813_3020101:8563_3030101:685008_9101:171252</t>
+  </si>
+  <si>
+    <t>3010101:44870_3020101:8974_3030101:717920_9101:179480</t>
+  </si>
+  <si>
+    <t>3010101:47133_3020101:9427_3030101:754120_9101:188530</t>
+  </si>
+  <si>
+    <t>3010101:49486_3020101:9897_3030101:791768_9101:197942</t>
+  </si>
+  <si>
+    <t>3010101:51933_3020101:10387_3030101:830920_9101:207730</t>
+  </si>
+  <si>
+    <t>3010101:54478_3020101:10896_3030101:871640_9101:217910</t>
+  </si>
+  <si>
+    <t>3010101:57125_3020101:11425_3030101:913992_9101:228498</t>
+  </si>
+  <si>
+    <t>3010101:59878_3020101:11976_3030101:958040_9101:239510</t>
+  </si>
+  <si>
+    <t>3010101:62741_3020101:12548_3030101:1003848_9101:250962</t>
+  </si>
+  <si>
+    <t>3010101:65718_3020101:13144_3030101:1051488_9101:262872</t>
+  </si>
+  <si>
+    <t>3010101:68815_3020101:13763_3030101:1101032_9101:275258</t>
+  </si>
+  <si>
+    <t>3010101:72035_3020101:14407_3030101:1152560_9101:288140</t>
+  </si>
+  <si>
+    <t>3010101:75578_3020101:15116_3030101:1209240_9101:302310</t>
+  </si>
+  <si>
+    <t>3010101:79262_3020101:15852_3030101:1268184_9101:317046</t>
+  </si>
+  <si>
+    <t>3010101:83093_3020101:16619_3030101:1329488_9101:332372</t>
+  </si>
+  <si>
+    <t>3010101:87078_3020101:17416_3030101:1393248_9101:348312</t>
+  </si>
+  <si>
+    <t>3010101:91223_3020101:18245_3030101:1459560_9101:364890</t>
+  </si>
+  <si>
+    <t>3010101:95533_3020101:19107_3030101:1528528_9101:382132</t>
+  </si>
+  <si>
+    <t>3010101:100016_3020101:20003_3030101:1600256_9101:400064</t>
+  </si>
+  <si>
+    <t>3010101:104679_3020101:20936_3030101:1674856_9101:418714</t>
+  </si>
+  <si>
+    <t>3010101:109528_3020101:21906_3030101:1752440_9101:438110</t>
+  </si>
+  <si>
+    <t>3010101:114571_3020101:22914_3030101:1833128_9101:458282</t>
+  </si>
+  <si>
+    <t>3010101:120118_3020101:24024_3030101:1921888_9101:480472</t>
+  </si>
+  <si>
+    <t>3010101:125888_3020101:25178_3030101:2014200_9101:503550</t>
+  </si>
+  <si>
+    <t>3010101:131888_3020101:26378_3030101:2110208_9101:527552</t>
+  </si>
+  <si>
+    <t>3010101:138129_3020101:27626_3030101:2210056_9101:552514</t>
+  </si>
+  <si>
+    <t>3010101:144619_3020101:28924_3030101:2313896_9101:578474</t>
+  </si>
+  <si>
+    <t>3010101:151368_3020101:30274_3030101:2421888_9101:605472</t>
+  </si>
+  <si>
+    <t>3010101:158388_3020101:31678_3030101:2534200_9101:633550</t>
+  </si>
+  <si>
+    <t>3010101:165688_3020101:33138_3030101:2651008_9101:662752</t>
+  </si>
+  <si>
+    <t>3010101:173281_3020101:34656_3030101:2772488_9101:693122</t>
+  </si>
+  <si>
+    <t>3010101:181177_3020101:36235_3030101:2898824_9101:724706</t>
+  </si>
+  <si>
+    <t>3010101:189862_3020101:37972_3030101:3037792_9101:759448</t>
+  </si>
+  <si>
+    <t>3010101:198895_3020101:39779_3030101:3182320_9101:795580</t>
+  </si>
+  <si>
+    <t>3010101:208290_3020101:41658_3030101:3332632_9101:833158</t>
+  </si>
+  <si>
+    <t>3010101:218060_3020101:43612_3030101:3488960_9101:872240</t>
+  </si>
+  <si>
+    <t>3010101:228222_3020101:45644_3030101:3651544_9101:912886</t>
+  </si>
+  <si>
+    <t>3010101:238790_3020101:47758_3030101:3820632_9101:955158</t>
+  </si>
+  <si>
+    <t>3010101:249780_3020101:49956_3030101:3996480_9101:999120</t>
+  </si>
+  <si>
+    <t>3010101:261210_3020101:52242_3030101:4179360_9101:1044840</t>
+  </si>
+  <si>
+    <t>3010101:273097_3020101:54619_3030101:4369552_9101:1092388</t>
+  </si>
+  <si>
+    <t>3010101:285460_3020101:57092_3030101:4567352_9101:1141838</t>
+  </si>
+  <si>
+    <t>3010101:299059_3020101:59812_3030101:4784936_9101:1196234</t>
+  </si>
+  <si>
+    <t>3010101:313202_3020101:62640_3030101:5011224_9101:1252806</t>
+  </si>
+  <si>
+    <t>3010101:327910_3020101:65582_3030101:5246560_9101:1311640</t>
+  </si>
+  <si>
+    <t>3010101:343207_3020101:68641_3030101:5491312_9101:1372828</t>
+  </si>
+  <si>
+    <t>3010101:359116_3020101:71823_3030101:5745856_9101:1436464</t>
+  </si>
+  <si>
+    <t>3010101:375662_3020101:75132_3030101:6010584_9101:1502646</t>
+  </si>
+  <si>
+    <t>3010101:392869_3020101:78574_3030101:6285904_9101:1571476</t>
+  </si>
+  <si>
+    <t>3010101:410765_3020101:82153_3030101:6572240_9101:1643060</t>
+  </si>
+  <si>
+    <t>3010101:429377_3020101:85875_3030101:6870032_9101:1717508</t>
+  </si>
+  <si>
+    <t>3010101:448734_3020101:89747_3030101:7179736_9101:1794934</t>
+  </si>
+  <si>
+    <t>3010101:470026_3020101:94005_3030101:7520408_9101:1880102</t>
+  </si>
+  <si>
+    <t>3010101:492169_3020101:98434_3030101:7874704_9101:1968676</t>
+  </si>
+  <si>
+    <t>3010101:515198_3020101:103040_3030101:8243168_9101:2060792</t>
+  </si>
+  <si>
+    <t>3010101:539148_3020101:107830_3030101:8626368_9101:2156592</t>
+  </si>
+  <si>
+    <t>3010101:564056_3020101:112811_3030101:9024896_9101:2256224</t>
+  </si>
+  <si>
+    <t>3010101:589961_3020101:117992_3030101:9439368_9101:2359842</t>
+  </si>
+  <si>
+    <t>3010101:616901_3020101:123380_3030101:9870416_9101:2467604</t>
+  </si>
+  <si>
+    <t>3010101:644919_3020101:128984_3030101:10318704_9101:2579676</t>
+  </si>
+  <si>
+    <t>3010101:674058_3020101:134812_3030101:10784920_9101:2696230</t>
+  </si>
+  <si>
+    <t>3010101:704362_3020101:140872_3030101:11269784_9101:2817446</t>
+  </si>
+  <si>
+    <t>3010101:737696_3020101:147539_3030101:11803136_9101:2950784</t>
+  </si>
+  <si>
+    <t>3010101:772364_3020101:154473_3030101:12357824_9101:3089456</t>
+  </si>
+  <si>
+    <t>3010101:808419_3020101:161684_3030101:12934696_9101:3233674</t>
+  </si>
+  <si>
+    <t>3010101:845915_3020101:169183_3030101:13534640_9101:3383660</t>
+  </si>
+  <si>
+    <t>3010101:884912_3020101:176982_3030101:14158584_9101:3539646</t>
+  </si>
+  <si>
+    <t>3010101:925468_3020101:185094_3030101:14807488_9101:3701872</t>
+  </si>
+  <si>
+    <t>3010101:967647_3020101:193529_3030101:15482352_9101:3870588</t>
+  </si>
+  <si>
+    <t>3010101:1011513_3020101:202303_3030101:16184208_9101:4046052</t>
+  </si>
+  <si>
+    <t>3010101:1057134_3020101:211427_3030101:16914136_9101:4228534</t>
+  </si>
+  <si>
+    <t>3010101:1104579_3020101:220916_3030101:17673264_9101:4418316</t>
+  </si>
+  <si>
+    <t>3010101:1156769_3020101:231354_3030101:18508304_9101:4627076</t>
+  </si>
+  <si>
+    <t>3010101:1211047_3020101:242209_3030101:19376744_9101:4844186</t>
+  </si>
+  <si>
+    <t>3010101:1267495_3020101:253499_3030101:20279920_9101:5069980</t>
+  </si>
+  <si>
+    <t>3010101:1326202_3020101:265240_3030101:21219224_9101:5304806</t>
+  </si>
+  <si>
+    <t>3010101:1387257_3020101:277451_3030101:22196104_9101:5549026</t>
+  </si>
+  <si>
+    <t>3010101:1450754_3020101:290151_3030101:23212056_9101:5803014</t>
+  </si>
+  <si>
+    <t>3010101:1516791_3020101:303358_3030101:24268648_9101:6067162</t>
+  </si>
+  <si>
+    <t>3010101:1585469_3020101:317094_3030101:25367504_9101:6341876</t>
+  </si>
+  <si>
+    <t>3010101:1656895_3020101:331379_3030101:26510312_9101:6627578</t>
+  </si>
+  <si>
+    <t>3010101:1731177_3020101:346235_3030101:27698832_9101:6924708</t>
+  </si>
+  <si>
+    <t>3010101:1812888_3020101:362578_3030101:29006208_9101:7251552</t>
+  </si>
+  <si>
+    <t>3010101:1897868_3020101:379574_3030101:30365880_9101:7591470</t>
+  </si>
+  <si>
+    <t>3010101:1986246_3020101:397249_3030101:31779936_9101:7944984</t>
+  </si>
+  <si>
+    <t>3010101:2078160_3020101:415632_3030101:33250552_9101:8312638</t>
+  </si>
+  <si>
+    <t>3010101:2173750_3020101:434750_3030101:34779992_9101:8694998</t>
+  </si>
+  <si>
+    <t>3010101:2273163_3020101:454633_3030101:36370608_9101:9092652</t>
+  </si>
+  <si>
+    <t>3010101:2376553_3020101:475311_3030101:38024848_9101:9506212</t>
+  </si>
+  <si>
+    <t>3010101:2484079_3020101:496816_3030101:39745256_9101:9936314</t>
+  </si>
+  <si>
+    <t>3010101:2595905_3020101:519181_3030101:41534480_9101:10383620</t>
+  </si>
+  <si>
+    <t>3010101:2712205_3020101:542441_3030101:43395272_9101:10848818</t>
   </si>
 </sst>
 </file>

--- a/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_level_v8【迷宫-探险等级】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B07DB6-6B15-469A-85EE-0C9938A8847F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE0404D-EC8A-44EC-B93B-5CD3C6CA4CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_level_v8" sheetId="1" r:id="rId1"/>
@@ -85,481 +85,481 @@
     <t>3010101:5_3020101:1_3030101:80_9101:20</t>
   </si>
   <si>
-    <t>3010101:14_3020101:3_3030101:224_9101:56</t>
-  </si>
-  <si>
-    <t>3010101:29_3020101:6_3030101:464_9101:116</t>
-  </si>
-  <si>
     <t>3010101:52_3020101:10_3030101:824_9101:206</t>
   </si>
   <si>
-    <t>3010101:83_3020101:17_3030101:1328_9101:332</t>
-  </si>
-  <si>
-    <t>3010101:125_3020101:25_3030101:1992_9101:498</t>
-  </si>
-  <si>
-    <t>3010101:176_3020101:35_3030101:2816_9101:704</t>
-  </si>
-  <si>
-    <t>3010101:238_3020101:48_3030101:3800_9101:950</t>
-  </si>
-  <si>
-    <t>3010101:309_3020101:62_3030101:4944_9101:1236</t>
-  </si>
-  <si>
-    <t>3010101:391_3020101:78_3030101:6248_9101:1562</t>
-  </si>
-  <si>
-    <t>3010101:497_3020101:99_3030101:7952_9101:1988</t>
-  </si>
-  <si>
-    <t>3010101:615_3020101:123_3030101:9832_9101:2458</t>
-  </si>
-  <si>
-    <t>3010101:743_3020101:149_3030101:11888_9101:2972</t>
-  </si>
-  <si>
-    <t>3010101:883_3020101:177_3030101:14120_9101:3530</t>
-  </si>
-  <si>
-    <t>3010101:1033_3020101:207_3030101:16528_9101:4132</t>
-  </si>
-  <si>
-    <t>3010101:1195_3020101:239_3030101:19112_9101:4778</t>
-  </si>
-  <si>
-    <t>3010101:1367_3020101:273_3030101:21872_9101:5468</t>
-  </si>
-  <si>
-    <t>3010101:1551_3020101:310_3030101:24808_9101:6202</t>
-  </si>
-  <si>
-    <t>3010101:1745_3020101:349_3030101:27920_9101:6980</t>
-  </si>
-  <si>
-    <t>3010101:1951_3020101:390_3030101:31208_9101:7802</t>
-  </si>
-  <si>
-    <t>3010101:2184_3020101:437_3030101:34936_9101:8734</t>
-  </si>
-  <si>
-    <t>3010101:2429_3020101:486_3030101:38856_9101:9714</t>
-  </si>
-  <si>
-    <t>3010101:2686_3020101:537_3030101:42968_9101:10742</t>
-  </si>
-  <si>
-    <t>3010101:2955_3020101:591_3030101:47272_9101:11818</t>
-  </si>
-  <si>
-    <t>3010101:3236_3020101:647_3030101:51768_9101:12942</t>
-  </si>
-  <si>
-    <t>3010101:3529_3020101:706_3030101:56456_9101:14114</t>
-  </si>
-  <si>
-    <t>3010101:3834_3020101:767_3030101:61336_9101:15334</t>
-  </si>
-  <si>
-    <t>3010101:4151_3020101:830_3030101:66408_9101:16602</t>
-  </si>
-  <si>
-    <t>3010101:4480_3020101:896_3030101:71680_9101:17920</t>
-  </si>
-  <si>
-    <t>3010101:4823_3020101:965_3030101:77160_9101:19290</t>
-  </si>
-  <si>
-    <t>3010101:5200_3020101:1040_3030101:83192_9101:20798</t>
-  </si>
-  <si>
-    <t>3010101:5592_3020101:1118_3030101:89464_9101:22366</t>
-  </si>
-  <si>
-    <t>3010101:5999_3020101:1200_3030101:95984_9101:23996</t>
-  </si>
-  <si>
-    <t>3010101:6423_3020101:1285_3030101:102768_9101:25692</t>
-  </si>
-  <si>
-    <t>3010101:6864_3020101:1373_3030101:109824_9101:27456</t>
-  </si>
-  <si>
-    <t>3010101:7323_3020101:1465_3030101:117160_9101:29290</t>
-  </si>
-  <si>
-    <t>3010101:7800_3020101:1560_3030101:124792_9101:31198</t>
-  </si>
-  <si>
-    <t>3010101:8296_3020101:1659_3030101:132728_9101:33182</t>
-  </si>
-  <si>
-    <t>3010101:8812_3020101:1762_3030101:140984_9101:35246</t>
-  </si>
-  <si>
-    <t>3010101:9348_3020101:1870_3030101:149568_9101:37392</t>
-  </si>
-  <si>
-    <t>3010101:9938_3020101:1988_3030101:159008_9101:39752</t>
-  </si>
-  <si>
-    <t>3010101:10552_3020101:2110_3030101:168824_9101:42206</t>
-  </si>
-  <si>
-    <t>3010101:11190_3020101:2238_3030101:179032_9101:44758</t>
-  </si>
-  <si>
-    <t>3010101:11853_3020101:2371_3030101:189648_9101:47412</t>
-  </si>
-  <si>
-    <t>3010101:12543_3020101:2509_3030101:200688_9101:50172</t>
-  </si>
-  <si>
-    <t>3010101:13261_3020101:2652_3030101:212168_9101:53042</t>
-  </si>
-  <si>
-    <t>3010101:14007_3020101:2801_3030101:224104_9101:56026</t>
-  </si>
-  <si>
-    <t>3010101:14783_3020101:2957_3030101:236520_9101:59130</t>
-  </si>
-  <si>
-    <t>3010101:15590_3020101:3118_3030101:249432_9101:62358</t>
-  </si>
-  <si>
-    <t>3010101:16429_3020101:3286_3030101:262864_9101:65716</t>
-  </si>
-  <si>
-    <t>3010101:17353_3020101:3471_3030101:277640_9101:69410</t>
-  </si>
-  <si>
-    <t>3010101:18313_3020101:3663_3030101:293008_9101:73252</t>
-  </si>
-  <si>
-    <t>3010101:19312_3020101:3862_3030101:308992_9101:77248</t>
-  </si>
-  <si>
-    <t>3010101:20351_3020101:4070_3030101:325616_9101:81404</t>
-  </si>
-  <si>
-    <t>3010101:21432_3020101:4286_3030101:342904_9101:85726</t>
-  </si>
-  <si>
-    <t>3010101:22555_3020101:4511_3030101:360880_9101:90220</t>
-  </si>
-  <si>
-    <t>3010101:23724_3020101:4745_3030101:379576_9101:94894</t>
-  </si>
-  <si>
-    <t>3010101:24939_3020101:4988_3030101:399016_9101:99754</t>
-  </si>
-  <si>
-    <t>3010101:26202_3020101:5240_3030101:419232_9101:104808</t>
-  </si>
-  <si>
-    <t>3010101:27516_3020101:5503_3030101:440256_9101:110064</t>
-  </si>
-  <si>
-    <t>3010101:28962_3020101:5792_3030101:463384_9101:115846</t>
-  </si>
-  <si>
-    <t>3010101:30465_3020101:6093_3030101:487440_9101:121860</t>
-  </si>
-  <si>
-    <t>3010101:32029_3020101:6406_3030101:512456_9101:128114</t>
-  </si>
-  <si>
-    <t>3010101:33655_3020101:6731_3030101:538472_9101:134618</t>
-  </si>
-  <si>
-    <t>3010101:35346_3020101:7069_3030101:565528_9101:141382</t>
-  </si>
-  <si>
-    <t>3010101:37104_3020101:7421_3030101:593664_9101:148416</t>
-  </si>
-  <si>
-    <t>3010101:38933_3020101:7787_3030101:622928_9101:155732</t>
-  </si>
-  <si>
-    <t>3010101:40835_3020101:8167_3030101:653360_9101:163340</t>
-  </si>
-  <si>
-    <t>3010101:42813_3020101:8563_3030101:685008_9101:171252</t>
-  </si>
-  <si>
-    <t>3010101:44870_3020101:8974_3030101:717920_9101:179480</t>
-  </si>
-  <si>
-    <t>3010101:47133_3020101:9427_3030101:754120_9101:188530</t>
-  </si>
-  <si>
-    <t>3010101:49486_3020101:9897_3030101:791768_9101:197942</t>
-  </si>
-  <si>
-    <t>3010101:51933_3020101:10387_3030101:830920_9101:207730</t>
-  </si>
-  <si>
-    <t>3010101:54478_3020101:10896_3030101:871640_9101:217910</t>
-  </si>
-  <si>
-    <t>3010101:57125_3020101:11425_3030101:913992_9101:228498</t>
-  </si>
-  <si>
-    <t>3010101:59878_3020101:11976_3030101:958040_9101:239510</t>
-  </si>
-  <si>
-    <t>3010101:62741_3020101:12548_3030101:1003848_9101:250962</t>
-  </si>
-  <si>
-    <t>3010101:65718_3020101:13144_3030101:1051488_9101:262872</t>
-  </si>
-  <si>
-    <t>3010101:68815_3020101:13763_3030101:1101032_9101:275258</t>
-  </si>
-  <si>
-    <t>3010101:72035_3020101:14407_3030101:1152560_9101:288140</t>
-  </si>
-  <si>
-    <t>3010101:75578_3020101:15116_3030101:1209240_9101:302310</t>
-  </si>
-  <si>
-    <t>3010101:79262_3020101:15852_3030101:1268184_9101:317046</t>
-  </si>
-  <si>
-    <t>3010101:83093_3020101:16619_3030101:1329488_9101:332372</t>
-  </si>
-  <si>
-    <t>3010101:87078_3020101:17416_3030101:1393248_9101:348312</t>
-  </si>
-  <si>
-    <t>3010101:91223_3020101:18245_3030101:1459560_9101:364890</t>
-  </si>
-  <si>
-    <t>3010101:95533_3020101:19107_3030101:1528528_9101:382132</t>
-  </si>
-  <si>
-    <t>3010101:100016_3020101:20003_3030101:1600256_9101:400064</t>
-  </si>
-  <si>
-    <t>3010101:104679_3020101:20936_3030101:1674856_9101:418714</t>
-  </si>
-  <si>
-    <t>3010101:109528_3020101:21906_3030101:1752440_9101:438110</t>
-  </si>
-  <si>
-    <t>3010101:114571_3020101:22914_3030101:1833128_9101:458282</t>
-  </si>
-  <si>
-    <t>3010101:120118_3020101:24024_3030101:1921888_9101:480472</t>
-  </si>
-  <si>
-    <t>3010101:125888_3020101:25178_3030101:2014200_9101:503550</t>
-  </si>
-  <si>
-    <t>3010101:131888_3020101:26378_3030101:2110208_9101:527552</t>
-  </si>
-  <si>
-    <t>3010101:138129_3020101:27626_3030101:2210056_9101:552514</t>
-  </si>
-  <si>
-    <t>3010101:144619_3020101:28924_3030101:2313896_9101:578474</t>
-  </si>
-  <si>
-    <t>3010101:151368_3020101:30274_3030101:2421888_9101:605472</t>
-  </si>
-  <si>
-    <t>3010101:158388_3020101:31678_3030101:2534200_9101:633550</t>
-  </si>
-  <si>
-    <t>3010101:165688_3020101:33138_3030101:2651008_9101:662752</t>
-  </si>
-  <si>
-    <t>3010101:173281_3020101:34656_3030101:2772488_9101:693122</t>
-  </si>
-  <si>
-    <t>3010101:181177_3020101:36235_3030101:2898824_9101:724706</t>
-  </si>
-  <si>
-    <t>3010101:189862_3020101:37972_3030101:3037792_9101:759448</t>
-  </si>
-  <si>
-    <t>3010101:198895_3020101:39779_3030101:3182320_9101:795580</t>
-  </si>
-  <si>
-    <t>3010101:208290_3020101:41658_3030101:3332632_9101:833158</t>
-  </si>
-  <si>
-    <t>3010101:218060_3020101:43612_3030101:3488960_9101:872240</t>
-  </si>
-  <si>
-    <t>3010101:228222_3020101:45644_3030101:3651544_9101:912886</t>
-  </si>
-  <si>
-    <t>3010101:238790_3020101:47758_3030101:3820632_9101:955158</t>
-  </si>
-  <si>
-    <t>3010101:249780_3020101:49956_3030101:3996480_9101:999120</t>
-  </si>
-  <si>
-    <t>3010101:261210_3020101:52242_3030101:4179360_9101:1044840</t>
-  </si>
-  <si>
-    <t>3010101:273097_3020101:54619_3030101:4369552_9101:1092388</t>
-  </si>
-  <si>
-    <t>3010101:285460_3020101:57092_3030101:4567352_9101:1141838</t>
-  </si>
-  <si>
-    <t>3010101:299059_3020101:59812_3030101:4784936_9101:1196234</t>
-  </si>
-  <si>
-    <t>3010101:313202_3020101:62640_3030101:5011224_9101:1252806</t>
-  </si>
-  <si>
-    <t>3010101:327910_3020101:65582_3030101:5246560_9101:1311640</t>
-  </si>
-  <si>
-    <t>3010101:343207_3020101:68641_3030101:5491312_9101:1372828</t>
-  </si>
-  <si>
-    <t>3010101:359116_3020101:71823_3030101:5745856_9101:1436464</t>
-  </si>
-  <si>
-    <t>3010101:375662_3020101:75132_3030101:6010584_9101:1502646</t>
-  </si>
-  <si>
-    <t>3010101:392869_3020101:78574_3030101:6285904_9101:1571476</t>
-  </si>
-  <si>
-    <t>3010101:410765_3020101:82153_3030101:6572240_9101:1643060</t>
-  </si>
-  <si>
-    <t>3010101:429377_3020101:85875_3030101:6870032_9101:1717508</t>
-  </si>
-  <si>
-    <t>3010101:448734_3020101:89747_3030101:7179736_9101:1794934</t>
-  </si>
-  <si>
-    <t>3010101:470026_3020101:94005_3030101:7520408_9101:1880102</t>
-  </si>
-  <si>
-    <t>3010101:492169_3020101:98434_3030101:7874704_9101:1968676</t>
-  </si>
-  <si>
-    <t>3010101:515198_3020101:103040_3030101:8243168_9101:2060792</t>
-  </si>
-  <si>
-    <t>3010101:539148_3020101:107830_3030101:8626368_9101:2156592</t>
-  </si>
-  <si>
-    <t>3010101:564056_3020101:112811_3030101:9024896_9101:2256224</t>
-  </si>
-  <si>
-    <t>3010101:589961_3020101:117992_3030101:9439368_9101:2359842</t>
-  </si>
-  <si>
-    <t>3010101:616901_3020101:123380_3030101:9870416_9101:2467604</t>
-  </si>
-  <si>
-    <t>3010101:644919_3020101:128984_3030101:10318704_9101:2579676</t>
-  </si>
-  <si>
-    <t>3010101:674058_3020101:134812_3030101:10784920_9101:2696230</t>
-  </si>
-  <si>
-    <t>3010101:704362_3020101:140872_3030101:11269784_9101:2817446</t>
-  </si>
-  <si>
-    <t>3010101:737696_3020101:147539_3030101:11803136_9101:2950784</t>
-  </si>
-  <si>
-    <t>3010101:772364_3020101:154473_3030101:12357824_9101:3089456</t>
-  </si>
-  <si>
-    <t>3010101:808419_3020101:161684_3030101:12934696_9101:3233674</t>
-  </si>
-  <si>
-    <t>3010101:845915_3020101:169183_3030101:13534640_9101:3383660</t>
-  </si>
-  <si>
-    <t>3010101:884912_3020101:176982_3030101:14158584_9101:3539646</t>
-  </si>
-  <si>
-    <t>3010101:925468_3020101:185094_3030101:14807488_9101:3701872</t>
-  </si>
-  <si>
-    <t>3010101:967647_3020101:193529_3030101:15482352_9101:3870588</t>
-  </si>
-  <si>
-    <t>3010101:1011513_3020101:202303_3030101:16184208_9101:4046052</t>
-  </si>
-  <si>
-    <t>3010101:1057134_3020101:211427_3030101:16914136_9101:4228534</t>
-  </si>
-  <si>
-    <t>3010101:1104579_3020101:220916_3030101:17673264_9101:4418316</t>
-  </si>
-  <si>
-    <t>3010101:1156769_3020101:231354_3030101:18508304_9101:4627076</t>
-  </si>
-  <si>
-    <t>3010101:1211047_3020101:242209_3030101:19376744_9101:4844186</t>
-  </si>
-  <si>
-    <t>3010101:1267495_3020101:253499_3030101:20279920_9101:5069980</t>
-  </si>
-  <si>
-    <t>3010101:1326202_3020101:265240_3030101:21219224_9101:5304806</t>
-  </si>
-  <si>
-    <t>3010101:1387257_3020101:277451_3030101:22196104_9101:5549026</t>
-  </si>
-  <si>
-    <t>3010101:1450754_3020101:290151_3030101:23212056_9101:5803014</t>
-  </si>
-  <si>
-    <t>3010101:1516791_3020101:303358_3030101:24268648_9101:6067162</t>
-  </si>
-  <si>
-    <t>3010101:1585469_3020101:317094_3030101:25367504_9101:6341876</t>
-  </si>
-  <si>
-    <t>3010101:1656895_3020101:331379_3030101:26510312_9101:6627578</t>
-  </si>
-  <si>
-    <t>3010101:1731177_3020101:346235_3030101:27698832_9101:6924708</t>
-  </si>
-  <si>
-    <t>3010101:1812888_3020101:362578_3030101:29006208_9101:7251552</t>
-  </si>
-  <si>
-    <t>3010101:1897868_3020101:379574_3030101:30365880_9101:7591470</t>
-  </si>
-  <si>
-    <t>3010101:1986246_3020101:397249_3030101:31779936_9101:7944984</t>
-  </si>
-  <si>
-    <t>3010101:2078160_3020101:415632_3030101:33250552_9101:8312638</t>
-  </si>
-  <si>
-    <t>3010101:2173750_3020101:434750_3030101:34779992_9101:8694998</t>
-  </si>
-  <si>
-    <t>3010101:2273163_3020101:454633_3030101:36370608_9101:9092652</t>
-  </si>
-  <si>
-    <t>3010101:2376553_3020101:475311_3030101:38024848_9101:9506212</t>
-  </si>
-  <si>
-    <t>3010101:2484079_3020101:496816_3030101:39745256_9101:9936314</t>
-  </si>
-  <si>
-    <t>3010101:2595905_3020101:519181_3030101:41534480_9101:10383620</t>
-  </si>
-  <si>
-    <t>3010101:2712205_3020101:542441_3030101:43395272_9101:10848818</t>
+    <t>3010101:9_3020101:2_3030101:144_9101:36</t>
+  </si>
+  <si>
+    <t>3010101:15_3020101:3_3030101:240_9101:60</t>
+  </si>
+  <si>
+    <t>3010101:23_3020101:5_3030101:360_9101:90</t>
+  </si>
+  <si>
+    <t>3010101:32_3020101:6_3030101:504_9101:126</t>
+  </si>
+  <si>
+    <t>3010101:42_3020101:8_3030101:664_9101:166</t>
+  </si>
+  <si>
+    <t>3010101:62_3020101:12_3030101:984_9101:246</t>
+  </si>
+  <si>
+    <t>3010101:72_3020101:14_3030101:1144_9101:286</t>
+  </si>
+  <si>
+    <t>3010101:82_3020101:16_3030101:1304_9101:326</t>
+  </si>
+  <si>
+    <t>3010101:107_3020101:21_3030101:1704_9101:426</t>
+  </si>
+  <si>
+    <t>3010101:118_3020101:24_3030101:1880_9101:470</t>
+  </si>
+  <si>
+    <t>3010101:129_3020101:26_3030101:2056_9101:514</t>
+  </si>
+  <si>
+    <t>3010101:140_3020101:28_3030101:2232_9101:558</t>
+  </si>
+  <si>
+    <t>3010101:151_3020101:30_3030101:2408_9101:602</t>
+  </si>
+  <si>
+    <t>3010101:162_3020101:32_3030101:2584_9101:646</t>
+  </si>
+  <si>
+    <t>3010101:173_3020101:35_3030101:2760_9101:690</t>
+  </si>
+  <si>
+    <t>3010101:184_3020101:37_3030101:2936_9101:734</t>
+  </si>
+  <si>
+    <t>3010101:195_3020101:39_3030101:3112_9101:778</t>
+  </si>
+  <si>
+    <t>3010101:206_3020101:41_3030101:3288_9101:822</t>
+  </si>
+  <si>
+    <t>3010101:233_3020101:47_3030101:3728_9101:932</t>
+  </si>
+  <si>
+    <t>3010101:245_3020101:49_3030101:3920_9101:980</t>
+  </si>
+  <si>
+    <t>3010101:257_3020101:51_3030101:4112_9101:1028</t>
+  </si>
+  <si>
+    <t>3010101:269_3020101:54_3030101:4304_9101:1076</t>
+  </si>
+  <si>
+    <t>3010101:281_3020101:56_3030101:4496_9101:1124</t>
+  </si>
+  <si>
+    <t>3010101:293_3020101:59_3030101:4688_9101:1172</t>
+  </si>
+  <si>
+    <t>3010101:305_3020101:61_3030101:4880_9101:1220</t>
+  </si>
+  <si>
+    <t>3010101:317_3020101:63_3030101:5072_9101:1268</t>
+  </si>
+  <si>
+    <t>3010101:330_3020101:66_3030101:5272_9101:1318</t>
+  </si>
+  <si>
+    <t>3010101:343_3020101:69_3030101:5480_9101:1370</t>
+  </si>
+  <si>
+    <t>3010101:377_3020101:75_3030101:6032_9101:1508</t>
+  </si>
+  <si>
+    <t>3010101:392_3020101:78_3030101:6272_9101:1568</t>
+  </si>
+  <si>
+    <t>3010101:408_3020101:82_3030101:6520_9101:1630</t>
+  </si>
+  <si>
+    <t>3010101:424_3020101:85_3030101:6784_9101:1696</t>
+  </si>
+  <si>
+    <t>3010101:441_3020101:88_3030101:7056_9101:1764</t>
+  </si>
+  <si>
+    <t>3010101:459_3020101:92_3030101:7336_9101:1834</t>
+  </si>
+  <si>
+    <t>3010101:477_3020101:95_3030101:7632_9101:1908</t>
+  </si>
+  <si>
+    <t>3010101:496_3020101:99_3030101:7936_9101:1984</t>
+  </si>
+  <si>
+    <t>3010101:516_3020101:103_3030101:8256_9101:2064</t>
+  </si>
+  <si>
+    <t>3010101:537_3020101:107_3030101:8584_9101:2146</t>
+  </si>
+  <si>
+    <t>3010101:590_3020101:118_3030101:9440_9101:2360</t>
+  </si>
+  <si>
+    <t>3010101:614_3020101:123_3030101:9816_9101:2454</t>
+  </si>
+  <si>
+    <t>3010101:638_3020101:128_3030101:10208_9101:2552</t>
+  </si>
+  <si>
+    <t>3010101:664_3020101:133_3030101:10616_9101:2654</t>
+  </si>
+  <si>
+    <t>3010101:690_3020101:138_3030101:11040_9101:2760</t>
+  </si>
+  <si>
+    <t>3010101:718_3020101:144_3030101:11480_9101:2870</t>
+  </si>
+  <si>
+    <t>3010101:746_3020101:149_3030101:11936_9101:2984</t>
+  </si>
+  <si>
+    <t>3010101:776_3020101:155_3030101:12416_9101:3104</t>
+  </si>
+  <si>
+    <t>3010101:807_3020101:161_3030101:12912_9101:3228</t>
+  </si>
+  <si>
+    <t>3010101:840_3020101:168_3030101:13432_9101:3358</t>
+  </si>
+  <si>
+    <t>3010101:924_3020101:185_3030101:14776_9101:3694</t>
+  </si>
+  <si>
+    <t>3010101:961_3020101:192_3030101:15368_9101:3842</t>
+  </si>
+  <si>
+    <t>3010101:999_3020101:200_3030101:15984_9101:3996</t>
+  </si>
+  <si>
+    <t>3010101:1039_3020101:208_3030101:16624_9101:4156</t>
+  </si>
+  <si>
+    <t>3010101:1081_3020101:216_3030101:17288_9101:4322</t>
+  </si>
+  <si>
+    <t>3010101:1124_3020101:225_3030101:17976_9101:4494</t>
+  </si>
+  <si>
+    <t>3010101:1169_3020101:234_3030101:18696_9101:4674</t>
+  </si>
+  <si>
+    <t>3010101:1215_3020101:243_3030101:19440_9101:4860</t>
+  </si>
+  <si>
+    <t>3010101:1264_3020101:253_3030101:20216_9101:5054</t>
+  </si>
+  <si>
+    <t>3010101:1314_3020101:263_3030101:21024_9101:5256</t>
+  </si>
+  <si>
+    <t>3010101:1446_3020101:289_3030101:23128_9101:5782</t>
+  </si>
+  <si>
+    <t>3010101:1504_3020101:301_3030101:24056_9101:6014</t>
+  </si>
+  <si>
+    <t>3010101:1564_3020101:313_3030101:25016_9101:6254</t>
+  </si>
+  <si>
+    <t>3010101:1626_3020101:325_3030101:26016_9101:6504</t>
+  </si>
+  <si>
+    <t>3010101:1691_3020101:338_3030101:27056_9101:6764</t>
+  </si>
+  <si>
+    <t>3010101:1759_3020101:352_3030101:28136_9101:7034</t>
+  </si>
+  <si>
+    <t>3010101:1829_3020101:366_3030101:29264_9101:7316</t>
+  </si>
+  <si>
+    <t>3010101:1902_3020101:380_3030101:30432_9101:7608</t>
+  </si>
+  <si>
+    <t>3010101:1978_3020101:396_3030101:31648_9101:7912</t>
+  </si>
+  <si>
+    <t>3010101:2057_3020101:411_3030101:32912_9101:8228</t>
+  </si>
+  <si>
+    <t>3010101:2263_3020101:453_3030101:36200_9101:9050</t>
+  </si>
+  <si>
+    <t>3010101:2353_3020101:471_3030101:37648_9101:9412</t>
+  </si>
+  <si>
+    <t>3010101:2447_3020101:489_3030101:39152_9101:9788</t>
+  </si>
+  <si>
+    <t>3010101:2545_3020101:509_3030101:40720_9101:10180</t>
+  </si>
+  <si>
+    <t>3010101:2647_3020101:529_3030101:42352_9101:10588</t>
+  </si>
+  <si>
+    <t>3010101:2753_3020101:551_3030101:44048_9101:11012</t>
+  </si>
+  <si>
+    <t>3010101:2863_3020101:573_3030101:45808_9101:11452</t>
+  </si>
+  <si>
+    <t>3010101:2978_3020101:596_3030101:47640_9101:11910</t>
+  </si>
+  <si>
+    <t>3010101:3097_3020101:619_3030101:49544_9101:12386</t>
+  </si>
+  <si>
+    <t>3010101:3221_3020101:644_3030101:51528_9101:12882</t>
+  </si>
+  <si>
+    <t>3010101:3543_3020101:709_3030101:56680_9101:14170</t>
+  </si>
+  <si>
+    <t>3010101:3684_3020101:737_3030101:58944_9101:14736</t>
+  </si>
+  <si>
+    <t>3010101:3832_3020101:766_3030101:61304_9101:15326</t>
+  </si>
+  <si>
+    <t>3010101:3985_3020101:797_3030101:63760_9101:15940</t>
+  </si>
+  <si>
+    <t>3010101:4145_3020101:829_3030101:66312_9101:16578</t>
+  </si>
+  <si>
+    <t>3010101:4311_3020101:862_3030101:68968_9101:17242</t>
+  </si>
+  <si>
+    <t>3010101:4483_3020101:897_3030101:71728_9101:17932</t>
+  </si>
+  <si>
+    <t>3010101:4663_3020101:933_3030101:74600_9101:18650</t>
+  </si>
+  <si>
+    <t>3010101:4849_3020101:970_3030101:77584_9101:19396</t>
+  </si>
+  <si>
+    <t>3010101:5043_3020101:1009_3030101:80688_9101:20172</t>
+  </si>
+  <si>
+    <t>3010101:5548_3020101:1110_3030101:88760_9101:22190</t>
+  </si>
+  <si>
+    <t>3010101:5770_3020101:1154_3030101:92312_9101:23078</t>
+  </si>
+  <si>
+    <t>3010101:6001_3020101:1200_3030101:96008_9101:24002</t>
+  </si>
+  <si>
+    <t>3010101:6241_3020101:1248_3030101:99848_9101:24962</t>
+  </si>
+  <si>
+    <t>3010101:6490_3020101:1298_3030101:103840_9101:25960</t>
+  </si>
+  <si>
+    <t>3010101:6750_3020101:1350_3030101:107992_9101:26998</t>
+  </si>
+  <si>
+    <t>3010101:7020_3020101:1404_3030101:112312_9101:28078</t>
+  </si>
+  <si>
+    <t>3010101:7301_3020101:1460_3030101:116808_9101:29202</t>
+  </si>
+  <si>
+    <t>3010101:7593_3020101:1519_3030101:121480_9101:30370</t>
+  </si>
+  <si>
+    <t>3010101:7896_3020101:1579_3030101:126336_9101:31584</t>
+  </si>
+  <si>
+    <t>3010101:8686_3020101:1737_3030101:138968_9101:34742</t>
+  </si>
+  <si>
+    <t>3010101:9033_3020101:1807_3030101:144528_9101:36132</t>
+  </si>
+  <si>
+    <t>3010101:9395_3020101:1879_3030101:150312_9101:37578</t>
+  </si>
+  <si>
+    <t>3010101:9771_3020101:1954_3030101:156328_9101:39082</t>
+  </si>
+  <si>
+    <t>3010101:10162_3020101:2032_3030101:162584_9101:40646</t>
+  </si>
+  <si>
+    <t>3010101:10568_3020101:2114_3030101:169088_9101:42272</t>
+  </si>
+  <si>
+    <t>3010101:10991_3020101:2198_3030101:175848_9101:43962</t>
+  </si>
+  <si>
+    <t>3010101:11430_3020101:2286_3030101:182880_9101:45720</t>
+  </si>
+  <si>
+    <t>3010101:11887_3020101:2377_3030101:190192_9101:47548</t>
+  </si>
+  <si>
+    <t>3010101:12363_3020101:2473_3030101:197800_9101:49450</t>
+  </si>
+  <si>
+    <t>3010101:13599_3020101:2720_3030101:217584_9101:54396</t>
+  </si>
+  <si>
+    <t>3010101:14143_3020101:2829_3030101:226288_9101:56572</t>
+  </si>
+  <si>
+    <t>3010101:14709_3020101:2942_3030101:235336_9101:58834</t>
+  </si>
+  <si>
+    <t>3010101:15297_3020101:3059_3030101:244752_9101:61188</t>
+  </si>
+  <si>
+    <t>3010101:15909_3020101:3182_3030101:254544_9101:63636</t>
+  </si>
+  <si>
+    <t>3010101:16546_3020101:3309_3030101:264728_9101:66182</t>
+  </si>
+  <si>
+    <t>3010101:17208_3020101:3442_3030101:275320_9101:68830</t>
+  </si>
+  <si>
+    <t>3010101:17896_3020101:3579_3030101:286336_9101:71584</t>
+  </si>
+  <si>
+    <t>3010101:18612_3020101:3722_3030101:297792_9101:74448</t>
+  </si>
+  <si>
+    <t>3010101:19357_3020101:3871_3030101:309704_9101:77426</t>
+  </si>
+  <si>
+    <t>3010101:21292_3020101:4258_3030101:340672_9101:85168</t>
+  </si>
+  <si>
+    <t>3010101:22144_3020101:4429_3030101:354296_9101:88574</t>
+  </si>
+  <si>
+    <t>3010101:23029_3020101:4606_3030101:368464_9101:92116</t>
+  </si>
+  <si>
+    <t>3010101:23950_3020101:4790_3030101:383200_9101:95800</t>
+  </si>
+  <si>
+    <t>3010101:24908_3020101:4982_3030101:398528_9101:99632</t>
+  </si>
+  <si>
+    <t>3010101:25905_3020101:5181_3030101:414472_9101:103618</t>
+  </si>
+  <si>
+    <t>3010101:26941_3020101:5388_3030101:431048_9101:107762</t>
+  </si>
+  <si>
+    <t>3010101:28018_3020101:5604_3030101:448288_9101:112072</t>
+  </si>
+  <si>
+    <t>3010101:29139_3020101:5828_3030101:466216_9101:116554</t>
+  </si>
+  <si>
+    <t>3010101:30304_3020101:6061_3030101:484864_9101:121216</t>
+  </si>
+  <si>
+    <t>3010101:33335_3020101:6667_3030101:533352_9101:133338</t>
+  </si>
+  <si>
+    <t>3010101:34668_3020101:6934_3030101:554688_9101:138672</t>
+  </si>
+  <si>
+    <t>3010101:36055_3020101:7211_3030101:576872_9101:144218</t>
+  </si>
+  <si>
+    <t>3010101:37497_3020101:7499_3030101:599944_9101:149986</t>
+  </si>
+  <si>
+    <t>3010101:38997_3020101:7799_3030101:623944_9101:155986</t>
+  </si>
+  <si>
+    <t>3010101:40557_3020101:8111_3030101:648904_9101:162226</t>
+  </si>
+  <si>
+    <t>3010101:42179_3020101:8436_3030101:674864_9101:168716</t>
+  </si>
+  <si>
+    <t>3010101:43866_3020101:8773_3030101:701856_9101:175464</t>
+  </si>
+  <si>
+    <t>3010101:45621_3020101:9124_3030101:729928_9101:182482</t>
+  </si>
+  <si>
+    <t>3010101:47446_3020101:9489_3030101:759128_9101:189782</t>
+  </si>
+  <si>
+    <t>3010101:52190_3020101:10438_3030101:835040_9101:208760</t>
+  </si>
+  <si>
+    <t>3010101:54278_3020101:10856_3030101:868440_9101:217110</t>
+  </si>
+  <si>
+    <t>3010101:56449_3020101:11290_3030101:903176_9101:225794</t>
+  </si>
+  <si>
+    <t>3010101:58707_3020101:11741_3030101:939304_9101:234826</t>
+  </si>
+  <si>
+    <t>3010101:61055_3020101:12211_3030101:976880_9101:244220</t>
+  </si>
+  <si>
+    <t>3010101:63497_3020101:12699_3030101:1015952_9101:253988</t>
+  </si>
+  <si>
+    <t>3010101:66037_3020101:13207_3030101:1056592_9101:264148</t>
+  </si>
+  <si>
+    <t>3010101:68679_3020101:13736_3030101:1098856_9101:274714</t>
+  </si>
+  <si>
+    <t>3010101:71426_3020101:14285_3030101:1142808_9101:285702</t>
+  </si>
+  <si>
+    <t>3010101:74283_3020101:14857_3030101:1188520_9101:297130</t>
+  </si>
+  <si>
+    <t>3010101:81711_3020101:16342_3030101:1307376_9101:326844</t>
+  </si>
+  <si>
+    <t>3010101:84980_3020101:16996_3030101:1359672_9101:339918</t>
+  </si>
+  <si>
+    <t>3010101:88379_3020101:17676_3030101:1414056_9101:353514</t>
+  </si>
+  <si>
+    <t>3010101:91914_3020101:18383_3030101:1470616_9101:367654</t>
+  </si>
+  <si>
+    <t>3010101:95590_3020101:19118_3030101:1529440_9101:382360</t>
+  </si>
+  <si>
+    <t>3010101:99414_3020101:19883_3030101:1590616_9101:397654</t>
+  </si>
+  <si>
+    <t>3010101:103390_3020101:20678_3030101:1654240_9101:413560</t>
+  </si>
+  <si>
+    <t>3010101:107526_3020101:21505_3030101:1720408_9101:430102</t>
+  </si>
+  <si>
+    <t>3010101:111827_3020101:22365_3030101:1789224_9101:447306</t>
+  </si>
+  <si>
+    <t>3010101:116300_3020101:23260_3030101:1860792_9101:465198</t>
   </si>
 </sst>
 </file>
@@ -977,7 +977,7 @@
         <v>330</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -991,7 +991,7 @@
         <v>830</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1005,7 +1005,7 @@
         <v>1430</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1019,7 +1019,7 @@
         <v>2330</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1033,7 +1033,7 @@
         <v>3530</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1047,7 +1047,7 @@
         <v>5130</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
